--- a/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
+++ b/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
@@ -10,14 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover and contents" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 About CreditSwan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Sector assessment" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Multiples and benchmark" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Deal A" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Deal B" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Deal C" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Financing observations" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Assumptions and method" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Sector assessment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Multiples and benchmark" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Deal A" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Deal B" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Deal C" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Financing observations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Assumptions and method" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -626,163 +626,144 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>02 About CreditSwan</t>
+          <t>03 Sector assessment</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Part 02 — About CreditSwan</t>
+          <t>Part 03 — Sector assessment</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Part 02 — About CreditSwan</t>
+          <t>Assumptions used in Part 03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>03 Sector assessment</t>
+          <t>04 Multiples and benchmark</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Part 03 — Sector assessment</t>
+          <t>Part 04 — Multiples and benchmark</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 03</t>
+          <t>Assumptions used in Part 04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>04 Multiples and benchmark</t>
+          <t>05 Deal A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Part 04 — Multiples and benchmark</t>
+          <t>Part 05 — Deal A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 04</t>
+          <t>Assumptions used in Part 05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>05 Deal A</t>
+          <t>06 Deal B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Part 05 — Deal A</t>
+          <t>Part 06 — Deal B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 05</t>
+          <t>Assumptions used in Part 06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>06 Deal B</t>
+          <t>07 Deal C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 06 — Deal B</t>
+          <t>Part 07 — Deal C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 06</t>
+          <t>Assumptions used in Part 07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>07 Deal C</t>
+          <t>08 Financing observations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 07 — Deal C</t>
+          <t>Part 08 — Financing observations</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 07</t>
+          <t>Assumptions used in Part 08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>08 Financing observations</t>
+          <t>09 Assumptions and method</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 08 — Financing observations</t>
+          <t>Part 09 — Assumptions and method</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assumptions used in Part 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>09 Assumptions and method</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Part 09 — Assumptions and method</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>123</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>Exhibit 9.01 — The readings rest on 31 stated assumptions; the EBITDA rung alone moves the same first-lien debt between 3.4x and 20x at three comparator platforms</t>
         </is>
       </c>
     </row>
+    <row r="14"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -797,2267 +778,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Part 08 — Financing observations</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Assumptions used in Part 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Value used</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>A-12</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Every multiple states its earnings measure and the debt it counts</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Leverage from first-lien funded debt up to all debt with leases and supplier finance; multiples marked standalone or synergised</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>EBITDA is kept on named levels</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Reported, adjusted, pro forma, run-rate, underwriting and cash EBITDA (pro forma less "one-time" costs that recur)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>A-F11</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Operating case on the recapitalisation model</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>The model of 29 September as it stands: scenario 3, downside on, closure scenario off</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>A-F12</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Closure cash and fees on the recapitalisation model</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>$21.79m over 42.1 months from April 2027 and $4.3m of fees in the June 2027 quarter, funded on the revolver</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>A-F13</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Net closure benefit in the lead case</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>$2.9m a year from April 2027 (clinic EBITDA including co-op, operating leases run to term)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>A-F10</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Refinancing need</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Bank debt at September 2030 less cash above a $13m reserve</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.01 — On the evidence to October 2026, three financing readings are contradicted in whole or in part and one rests on missing terms; at Deal A the recapitalisation model repays supplier finance at close and liquidity is the tighter test, funding at Deal B is tested before the leverage covenant, and at Deal C Option Two's fixed-charge cover on cash EBITDA is below 1.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Our reading on the financing component of each thesis (M5, MS6, ST4 Option Two and Option One), with the depth of the evidence and what would change it; audited figures to FY26, models and term documents of September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>ABC Private Credit asked</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Our answer in brief</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Evidence behind it</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>What would change it</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Deal A: its scale and diversity make it compelling at a low leverage multiple (M5)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted as "resilient at low leverage"; partially supported as a sale-bridged loan. On the recapitalisation model of 29 September the $254m of funded debt is 3.51x gross first lien on the model's LTM 2Q27F EBITDA of $67.2m, and supplier finance is repaid at close; the leverage covenant peaks at 5.68x against 6.35x. With the company's closure cash and a $2.9m net closure benefit, minimum liquidity is $33.3m against a $21m minimum (March 2029), and a 4.05% EBITDA shortfall takes it below; the model's own fixed-charge cover is 0.76–1.03x from March 2027 to FY31 (Part 08 section B).</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Audited FY26 accounts and the June 2026 quarter (actual); the recapitalisation model of 29 September (projected), with a CreditSwan overlay for the company's closure cash and three closure-benefit cases; the 21 September term sheet, the only term sheet in the files.</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>July–September 2026 actuals; a term sheet on the model's structure, with its fixed-charge cover and liquidity tests; the closure cash budget and lease-exit plan; a third-party valuation of the owned real estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Deal B: a low-levered, high-priced deal with upside (MS6)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted — on trailing leverage, cover and funding. On ABC Private Credit's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>ABC Private Credit's response to the borrower's financing grid (19 September 2026) and the borrower's and ABC Private Credit's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>The agreed closing EBITDA and the measure it is struck on; cash at close; executed HoldCo terms; a sources-and-uses for the acquisition batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Deal C: the leverage requested is 5.3x (ST4, Option Two)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted. The $204.3m first lien is 5.96x gross on ABC Private Credit's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ABC Private Credit's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>The Accounting Firm 1 quality-of-earnings report; the affiliate-bonus agreements; August–September 2026 same-store EBITDA against the 1.57% threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Deal C: the leverage requested is 5.3x (ST4, Option One)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on ABC Private Credit's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>As for Option Two; the sponsor instrument's coupon, maturity, ranking and cash-pay terms are not in the documents supplied.</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>The sponsor instrument's coupon, maturity, ranking and cash-pay terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Source: Part 08 section B, Part 08 section C and Part 08 section D · Basis: Leverage on reported (A) and underwriting (P or PF) earnings as named; liquidity and refinancing from models (P)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.02 — Readings on the three proposed financings (to October 2026): Deal A's $254m on the recapitalisation model is 3.51x first lien and peaks at 5.68x on the lease-adjusted covenant, Deal B's stack reads 7.59x, and Deal C's 5.96x first lien sits above every 2025–26 same-rung print</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Reading label, basis, what holds, what does not and what would change it, for the financing component of each deal; leverage x, amounts $m; evidence supplied to 1 October 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Thesis component</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Our reading on the evidence supplied to date</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>What holds</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>What does not</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>What would change it</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Deal A</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>M5 · Low-leverage financing is resilient</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted as "resilient at low leverage"; partially supported as a sale-bridged loan</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>On the recapitalisation model of 29 September: $254m of funded debt, 3.51x gross and 2.80x net first lien on LTM 2Q27F EBITDA of $67.2m (P); adjusted gross debt ÷ EBITDAR peaks at 5.68x against 6.35x; with the workbook's closure cash and a $2.9m net benefit minimum liquidity is $33.3m against $21m, breached at a 4.05% EBITDA shortfall; the model's fixed-charge cover is 0.76–1.03x from March 2027 to FY31; at 4.3x the lead-case need of $257.8m is covered on reported LTM EBITDA (+$34.2m) and not on FY26 (−$8.6m) or on the model's LTM 2Q27F (−$33.9m) (Part 08 section B)</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; ABC Private Credit's Diligence &amp; Structure Update states that the sale process has been launched</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>A 4.05% EBITDA shortfall takes liquidity below $21m in the lead case, and 1.6% with no closure benefit; closure cash paid inside four quarters takes it to $19.5m ($15.1m with no benefit); the model's fixed-charge cover is below 1.0x from March 2027 to March 2028; at maturity the debt does not refinance at 4.3x on FY26 or on the model's own closing EBITDA</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>July–September 2026 actuals; a term sheet on the model's structure, with the fixed-charge cover and liquidity tests; the closure cash budget and lease-exit plan; a third-party valuation of the owned real estate, including the 26 sale-leaseback sites</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>MS6 · Low leverage, pricing and upside compensate</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted — on trailing leverage, cover and funding</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m (term loan $55m); fixed-charge cover 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on ABC Private Credit's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>The agreed closing EBITDA and rung; cash at close; executed HoldCo terms; a sources-and-uses for the batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>ST4 · 5.3x leverage is supportable — Option Two</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Contradicted</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>5.96x gross first lien on ABC Private Credit's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Cover computes at 0.96x on ABC Private Credit's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>The Accounting Firm 1 QoE; the affiliate-bonus agreements; August–September same-store EBITDA against the 1.57% threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>ST4 · 5.3x leverage is supportable — Option One</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Insufficient evidence — sponsor-instrument terms missing</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>5.30x gross first lien, outside the 3.81–5.10x band; 5.76x net incl. sponsor debt; debt service untestable without the sponsor terms; the refinancing result reverses with a 17% cash coupon (senior tranche) or a drawn delayed-draw loan (total debt) (Part 08 section D)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Cover computes at 1.00x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>The 5.30x gross first lien sits above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); the $21m sponsor instrument's coupon, maturity, ranking and cash-pay terms are not in the files; a 17% cash coupon on it reverses the senior result, and the delayed-draw loan drawn at the audited deal-cost rate leaves total debt short</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>The sponsor instrument's coupon, maturity, ranking and cash-pay terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Source: Leverage from first-lien funded debt to all debt with leases and supply-chain finance, and cash EBITDA after recurring deal costs, are defined in Part 09 section C · Basis: Figures as set out, with their references and bases (A, PF, P), in Part 08 section B, Part 08 section C and Part 08 section D</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in ABC Private Credit's model of September</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Main terms of the LW draft term sheet of 21 September 2026 (with ABC Private Credit's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>LW draft term sheet, 21 September 2026</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Recapitalisation model v06, 29 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Commitments</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>$336m: $111m super-senior revolver, $111m term loan, $111m delayed-draw term loan</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>$336m: $111m revolver, $218m term loan; no delayed-draw loan</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Drawn at close</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Revolver $44m deemed drawn; term loan $111m; ABC Private Credit's model v24: $152m of bank debt</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Revolver $44m (minimum draw $44m); term loan $218m; total debt $254.5m</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Supplier finance</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Unwound over 15 months through the delayed-draw loan, subject to a 5.15x draw test</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>$145m repaid at close; the remaining Lender 6 line winds down over six months</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Pricing and fees</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>S+5.26% term facilities; S+3.26% revolver, 21bp grid</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>S+5.26% term loan, 1% amortisation, 2% fee; S+3.26% revolver, 0.44% unused fee, 2% fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Sweeps</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>67% of excess cash flow</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>67% of excess cash flow; 100% of asset-sale proceeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Leverage at close</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>1.9x first lien on ABC Private Credit's $71.7m (LTM Sep-26, including a forecast quarter)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>3.51x gross, 2.80x net on LTM 2Q27F EBITDA of $64.45m</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Leverage covenant</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Lease-adjusted net leverage, 6.35x stepping to 5.81x</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Adjusted gross debt ÷ EBITDAR against a flat 6.35x on the Covenants tab (step-downs listed elsewhere in the model); peak 5.68x, March 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Minimum liquidity</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>$21.5m of average daily liquidity, tested quarterly</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>$21m input not referenced by any formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Fixed-charge cover</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>No maintenance test</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Labelled "≥1.08"; computes 0.76–1.03x from March 2027 to FY31</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Second-round closures</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>ABC Private Credit's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Closure scenario off: no benefit and no closure cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>December 2026 dividend</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>$7.4m permitted outside the payment conditions</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>$7.41m paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Close and maturity</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Calendar dates, not mapped to Deal A's fiscal quarters</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Close 14 October 2026; maturity 30 September 2030 on the drivers tab, 31 October 2030 on the capital-structure tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="52" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); ABC Private Credit Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Proposed debt at close (30 September 2026) ÷ EBITDA, x, gross, for the $55m and $52m term loans on six EBITDA denominators, with the peer comparison on the same rung</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Denominator (rung; basis; row block)</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>TL $55m: LV1 / LV3 / LV4</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>TL $52m: LV1 / LV3 / LV4</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Peer comparison on the same rung</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>E1 LTM Jul-26 $1.22m (A; DLB-9442 / 8012)</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>39.7x / 47.2x / 74.9x</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>38.2x / 44.5x / 72.4x</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Operator 6 LV1 on E1 as owned 16.59x (OP6-0034); Deal B above</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>E2 post-audit LTM Jul-26 $8.51m (PF; DLB-9424 / 8196)</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>5.58x / 6.55x / 10.43x</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>5.53x / 6.17x / 10.16x</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>No peer prints first-lien leverage on E2 alone; not placed</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>E5 ABC Private Credit LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>4.08x / 4.91x / 7.59x</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>3.91x / 4.53x / 7.77x</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5, 2025–26 same-rung set: Operator 7 2.25x (P), Operator 6 3.81x (PF closed), Operator 3 4.70x (P), Operator 4 5.10x on Lender 1's E5 (PF) (OP7-1181; OP6-0031; OP3-1326; OP4-1442): inside. LV4: Operator 8 5.4–5.68x net (OP8-2819/2452/2367), Operator 1 6.0–7.2x net (OP1-10738/10730): above all</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>E4 post-audit LTM Jul-26 $13.79m (PF; DLB-9406 / 8010)</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>3.41x / 3.94x / 6.38x</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>3.24x / 3.68x / 6.13x</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Operator 6 LV1 on buy-side QoE pro forma (E3) 4.84x (OP6-0032): below by 1.6–1.8x</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>E4 borrower LTM Sep-26E $14.77m (P; DLB-9370 / 8001)</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>3.28x / 3.71x / 5.99x</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>2.95x / 3.44x / 5.58x</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on financing EBITDA (E4/E5, the Exhibit 4.09 convention): 2025–26 same-rung set 2.25–5.10x inside; closed first-lien band since 2014 3.81–4.27x below</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>E5 borrower $16.1m incl. acquisitions (P; DLB-9388 / 8163)</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>2.84x / 3.30x / 5.39x</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>2.80x / 3.14x / 5.17x</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>as above: inside</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="39" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Source: DLB-026 (ABC Private Credit response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on ABC Private Credit's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>First-lien funded debt ÷ EBITDA, x, gross and net, by print and rung; Deal C at the September 2026 close, peers 2014 to 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Rung and basis</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Gross</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Locator</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Deal C Option Two (P)</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5 $29.4m, LTM Sep-26E</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>5.96x</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>5.92x</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>DLC-4725/4726</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Deal C Option One (P)</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>5.30x</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>5.10x</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>DLC-4872/4873</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Deal C Option One incl. $21m sponsor debt (P)</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>LV4 on E5</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>5.96x</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>5.76x</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>DLC-4878/4879</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Deal C FY25 legacy facilities (A)</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on D3 E1 / E2 / E3 / E3-E4 model</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>24.9x / 6.6x / 5.4x / 4.5x</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>22.5x / 6.2x / 5.1x / 4.3x</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>DLC-4459/4460; 3891/4502; 3977/4516; 3924/4544</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Operator 6, Jul-26 close (PF)</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>3.81x</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>OP6-0031</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Operator 3, Dec-25 proposal (P)</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>4.70x</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>OP3-1326</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Operator 4, Mar-26 (PF)</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on Lender 1 E5</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>5.10x</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>OP4-1442</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>Operator 7, 2026 proposal (P)</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E5 $8.8m</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>2.25x</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>1.97x</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>OP7-1181/1180</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Closed core prints, 2014–26</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on financing EBITDA (E4/E5)</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>median 4.3x (3.81–5.97x)</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>notes C-75 and C-76</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>Operator 2 Sponsor 1 LBO, Sep-21 (PF)</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>LV1 on E4</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>5.97x</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>6.05x</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>P5-S001; OP2-3732</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Operator 1, REOPEN21 / INFL22-23 (PF)</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>LV4 net on financing EBITDA</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>7.19x / 5.98x</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>OP1-10730; OP1-10738</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>Deal A, Operator 9, Operator 4 (A)</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>LV1 gross on D3 E1: Deal A FY26 / Operator 9 FY Sep-25 / Operator 4 FY24</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>0.62x / 6.32x / 8.60x</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DLA-0472; OP4-1464; OP4-1394</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>Source: rows as listed; Exhibit 9.75. Proposals (P) and closed prints are shown separately and not pooled · Basis: Deal C options P; legacy facilities A; peers PF, P or A as marked</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.16 — On the recapitalisation model the closure benefit's definition moves the EBITDA shortfall that takes Deal A's liquidity below $21m from 1.6% to 11.9%, and paying the closure cash inside four quarters takes the minimum below $21m; the leverage covenant is never the first signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Sensitivities that bear on the Deal A financing, set against observed ranges; CreditSwan overlay on the recapitalisation model v06 (29 September 2026); minimum quarter-end liquidity net of letters of credit, $m; refinancing at 30 September 2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Sensitivity</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>Result on the recapitalisation model</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Observed range (source)</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Reading on the observed range</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Closure benefit</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>No benefit $27.1m (below $21m at a 1.6% shortfall); $2.9m net benefit $33.3m (4.05%); management's $12m $37.0m (11.9%)</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Second-round cases of −$11.8m to +$20.4m a year, by measure of the benefit and lease exits (Part 05 section D)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Among the cases with closure cash paid as the leases run, the definition of the benefit moves the threshold from 1.6% to 11.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Timing of closure cash</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Over the remaining lease terms: $27.1m without benefit, $33.3m with it; inside four quarters: $15.1m and $19.5m</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Workbook costs run to lease end, 42.1 months on average; 30 of 109 leases end within 21 months (FY27 Closing Clinics Financial Analysis)</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Paid as the leases run, the minimum clears $21m; paid inside four quarters, for example to buy out leases, it does not</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>EBITDA shortfall</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Lead case below $21m at 4.05%; with no benefit and a 9% shortfall, liquidity below zero from December 2029 (−$14.1m by March 2031) and the leverage ratio peaks at 5.58x</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Deal A's own annual declines in reported EBITDA of 7.7–23.5% (FY23–FY26) and −34% year on year in company EBITDA in the first quarter of FY27 (Deal A 10-K FY23–FY26; bank model row 181)</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>The liquidity threshold lies inside Deal A's observed declines; the leverage covenant does not give the first signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>Leverage covenant level</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Peak 5.68x (lead) and 5.58x (9% shortfall) against a flat 6.35x; 0.67x of margin against the 6.13x step from June 2027 in the shortfall case</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>The model lists step-downs from 6.35x to 5.81x (Draw Schedule Summary row 101) but tests a flat 6.35x</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Which schedule applies is a point to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Refinancing multiple</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Lead-case need $257.8m at 30 September 2030</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Closed first-lien prints 3.81–4.27x (Operator 2's 2021 buyout at 5.97x aside), median 4.3x (Part 04 section B)</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>At 4.3x: +$34.2m on reported LTM EBITDA, −$8.6m on FY26, −$33.9m on the model's LTM 2Q27F; at 3.81x every actual rung falls short</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>Sale-leaseback</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Proceeds of $44.4m on the term loan take gross leverage on LTM 2Q27F EBITDA after the new rent from 3.51x to 3.06x</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>26 sites; 14 with a site loss in FY26; rent cover 1.23x on $3.44m of year-one rent rising 2.2% a year (Project Charlie I-Chart)</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Lowers funded debt, adds rent, and takes 26 sites out of the real estate behind recovery</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="39" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>Source: Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026); FY27 Closing Clinics Financial Analysis (DLA-027); Project Charlie I-Chart (DLA-029); notes C-V2-3 to C-V2-5; observed ranges as cited in each row · Basis: P for the model results [I]; A for the observed ranges unless marked · Assumption: A-F11, A-F12, A-F13, A-F10</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.17 — Deal B needs EBITDA above both current measures to refinance in December 2030 and its batch is $8.8–11.8m short; Deal C's Option Two needs at least 1.57% a year of EBITDA growth against +1.0% and −5.8% observed</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>Financing sensitivities of the Deal B and Deal C proposals: ABC Private Credit's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Deal</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Sensitivity</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>ABC Private Credit's case</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>What the evidence shows</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>Value tested</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Effect on the financing reading</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>EBITDA rung for leverage</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>2025–26 same-rung first-lien prints 2.25–5.10x (Operator 7 and Operator 3 proposals, Operator 6 closed, Operator 4 on Lender 1's E5); closed first-lien band since 2014 3.81–4.27x on financing EBITDA, Operator 2's 2021 5.97x aside; peer LV4 prints 5.4–7.2x (OP7-1181; OP6-0031; OP3-1326; OP4-1442; OP8-2819/2367; OP1-10730/10738)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>First lien 2.84x on the borrower's $16.1m to 5.58x on post-audit $8.51m; with the HoldCo 5.39x to 10.43x (DLB-9388..9391; DLB-9424..9427)</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on ABC Private Credit's EBITDA (Part 08 section C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Fixed-charge cover</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>FCCR_CD on ABC Private Credit's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Peer prints 0.7–1.6x on mixed definitions; association only (note C-80)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (ABC Private Credit's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Cover is about 1x on the borrower's EBITDA and below 1x on ABC Private Credit's; the peer prints are on different definitions, so no position is taken</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>HoldCo accretion, EBITDA flat for twelve months</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>HoldCo note of $36.9m at 15% PIK (DLB-5668)</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Contractual accretion to $44.0m by September 2027 (DLB-9111); peer LV4 prints 5.4–7.2x</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>Total leverage 7.85–8.25x on ABC Private Credit's $11.16m and 6.00–6.35x on $14.77m</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>With EBITDA flat, total leverage on ABC Private Credit's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Refinancing at December 2030</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>Senior debt of $79–82m and the HoldCo note at $73.3m at maturity (DLB-6246)</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Closed first-lien band 3.81–4.27x, median 4.3x (Exhibit 4.09); peer LV4 5.4–7.2x</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>EBITDA of $16.1–16.6m refinances the term loan and delayed-draw loan at 4.3x; $18.6–24.6m refinances them with the HoldCo at 5.4–7.2x</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Both thresholds sit above today's $11.16m on ABC Private Credit's measure and $13.79m post-audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Deal B</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Funding of the near-term batch</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (ABC Private Credit model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>The 23-unit batch needs a $47.5m delayed-draw draw (DLB-6069..6077)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>Residual shortfall $8.8m or $11.8m after the $4.3m liquidity floor (C-FIN-5)</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>On either model's closing cash the committed facilities leave the batch $8.8–11.8m short</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>EBITDA rung for leverage</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>Option Two's $204.3m first lien at 5.96x gross on ABC Private Credit's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>2025–26 same-rung prints 3.81–5.10x at Operator 6, Operator 3 and Operator 4, with Operator 7 2.25x proposal below; closed first-lien median 4.3x since 2014 (OP6-0031; OP3-1326; OP4-1442; OP7-1181; P5-S001)</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>Above every 2025–26 same-rung print and above the 4.3x closed median on every EBITDA measure in the files; among closed first-lien prints since 2014 only Operator 2's 2021 buyout (5.97x) is higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Fixed-charge cover</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>ABC Private Credit's coverage method on its cash EBITDA</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Cash breakeven EBITDA for Option Two $26.0m (DLC-4983)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Option Two 0.76x ($23.2m), 0.77x ($24.9m), 0.96x ($29.4m), 1.08x ($32.3m), 0.22x ($8.6m); Option One, term loan only at S+451: 1.00x ($24.9m), 1.23x ($29.4m), 1.37x ($32.3m) (DLC-4947..4982)</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Option Two covers its fixed charges only on EBITDA that includes forecast months</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Organic EBITDA growth to maturity</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Option Two on ABC Private Credit's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Same-store clinic EBITDA +1.0% for CY2025 and −5.8% for LTM July 2026 (DLC-0987; DLC-0996)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Gap at the 4.3x median: $23.0m flat, $7.5m at +1.0%, $101m at −5.8%; clears from 1.57% a year on $29.4m and 5.36% on $24.9m</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Refinancing needs growth above what Deal C's clinics delivered in the latest two periods</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Refinancing multiple</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>4.3x median of closed first-lien prints (notes C-75 and C-76)</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>3.81x (Operator 6, closed) to 5.10x (Operator 4 on E5); 3.38x as a stress</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Flat $29.4m clears only at 5.18x; gap of $53.0m at 3.38x</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>On flat earnings Option Two clears only at the top of the observed band</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>DDTL drawn</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>$70m DDTL for acquisitions, left undrawn on the no-acquisition path</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Deal costs 13.2% of price excluding affiliate bonuses ((DLC-0009 − DLC-0199) ÷ total consideration) and 31.2% on the audited rate (DLC-0009 ÷ total consideration of $32.8m, 2025 Audit Note 3, p.17)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>DDTL drawn at close, acquired EBITDA leverage-neutral (assumed)</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Option Two's gap at 4.3x on flat $29.4m widens from $23.0m to $35.7–51.5m; Option One's total debt misses by $8.0m at the audited rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>Deal C</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Sponsor instrument on cash pay</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>Option One's $21m sponsor instrument carried at face with no cash coupon; its terms are not in the files [U]</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>No coupon, maturity, ranking or cash-pay term in the files</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Cash coupon of 12% or 17% (assumed)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Option One's senior gap at 4.3x moves from −$23.9m to −$8.1m (10%) and +$2.3m (17%); its total gap to $13.4–23.4m</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="39" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>Source: Rows as cited in each cell; the underlying tables are Exhibit 8.10, Exhibit 9.162, Exhibit 9.164, Exhibit 9.165, Exhibit 9.166 and Exhibit 8.14; notes C-80, C-90 and C-FIN-5 · Basis: P for the proposed structures and every forward result; A or PF for the observed ranges as marked. All results [I] · Assumption: Growth rates other than Deal C's observed +1.0% and −5.8%, the 3.38x stress, the drawn DDTL and the sponsor coupons of 12% and 17% are assumed parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="45" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Exhibit 8.19 — Read against the recapitalisation model of 29 September, three of the fifteen observations fall away with the delayed-draw loan, two largely or partly fall away with supplier finance repaid at close, and fixed-charge cover and the untested liquidity minimum become the points to settle</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>Each observation on the LW draft term sheet (21 September 2026), with what the recapitalisation model v06 (29 September 2026) shows and its status; points to confirm in the model added</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Observation on the term sheet of 21 September</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>On the recapitalisation model of 29 September</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Leverage-ratio denominator: EBITDAR reading; stock compensation</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Computes on EBITDAR and adds back stock compensation ($6.2m LTM at March 2027, Covenants!J86); the term-sheet wording is still to settle</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Point to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Covenant levels well above the modelled path (4.53x peak on ABC Private Credit's model v24)</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>Peak 5.68x against 6.35x (1.0x of room); the Covenants tab shows a flat 6.35x, the Draw Schedule Summary step-downs to 5.81x (row 101)</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Holds, with less room</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Delayed-draw condition tested at each draw</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>No delayed-draw loan; supplier finance repaid at close</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Falls away</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Revolver cap while the delayed-draw loan is available</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>No delayed-draw loan</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>Falls away</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Letters of credit of at least $25.5m</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>The model carries $26m (Scenario Drivers!G23)</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Point to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Qualified Cash and control agreements</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>Not addressed in the model</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>December 2026 dividend outside the payment conditions; fixed-charge payment condition; run-rate add-backs</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>$7.41m paid in December 2026 (Draw Schedule Summary!J39); fixed-charge cover 0.77x at March 2027</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>EBITDAR clauses; disposal gains; closure-cash sub-cap</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per ABC Private Credit verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
-        <is>
-          <t>Point to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>Calendar against fiscal dates</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>Close 14 October 2026; maturity 30 September 2030 (Scenario Drivers!G77) against 31 October 2030 (PF Cap Structure!E11, E13)</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Point to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Supplier finance inside funded debt</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>$145m repaid at close; the remaining Lender 6 line winds down over six months (Scenario Drivers!G36)</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>Largely falls away</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Excess-cash-flow treatment of supplier-finance payments and delayed-draw proceeds</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>67% excess-cash sweep and 100% asset-sale sweep</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Partly falls away</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Prepayment premium on closure-programme proceeds</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged; now also bears on the sale-leaseback ($44.4–46.9m at Real Estate Advisor 1 values) under the 100% asset-sale sweep</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>Delayed-draw amortisation; debt carried in ABC Private Credit's model v24</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>No delayed-draw loan</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Falls away</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Conditions precedent; no mortgage provision</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged; the sale-leaseback would take 26 owned sites out of the real estate behind recovery</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>No fixed-charge cover maintenance test</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>Labelled "≥1.08"; the model's own path is 0.93x at December 2026 and 0.76–1.03x from March 2027 to FY31, below that level in every period were it a covenant</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Point to settle</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Points to confirm in the model</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>The $21m minimum liquidity input (Scenario Drivers!G31) is referenced by no formula; the first downside input (G32, $3.0m) is applied as $0.8m in the monthly P&amp;L (row 127), the other two ($2.6m, $5.9m) agree; Covenants!G85:I85 hard-code LTM EBITDA of $79.5m / $75.9m / $69.8m against the model's own $64.5m at December 2026 (Draw Schedule Summary!J106); the closure scenario is off; no sale-leaseback line</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>Points to confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="39" customHeight="1">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026), cells as cited in each row; the fifteen observations on the term sheet in Part 09 section O · Basis: Model terms and results as the model computes them [F]; projected (P). Statuses are our reading [I]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A76:D76"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50508,9 +48234,9 @@
     <mergeCell ref="A1495:D1495"/>
     <mergeCell ref="A1190:D1190"/>
     <mergeCell ref="A1795:D1795"/>
-    <mergeCell ref="A1633:F1633"/>
     <mergeCell ref="A805:H805"/>
     <mergeCell ref="A1697:H1697"/>
+    <mergeCell ref="A1633:F1633"/>
     <mergeCell ref="A792:H792"/>
     <mergeCell ref="A1206:F1206"/>
     <mergeCell ref="A1477:F1477"/>
@@ -50627,7 +48353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -50675,106 +48401,94 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>02 About CreditSwan</t>
+          <t>03 Sector assessment</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Who prepared this document and how the work is built</t>
+          <t>ABC Private Credit's six industry questions, (i) to (vi), one section each</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>03 Sector assessment</t>
+          <t>04 Multiples and benchmark</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's six industry questions, (i) to (vi), one section each</t>
+          <t>Valuation and leverage multiples over time, the benchmark of eleven operators, wellness clinics and emergency and specialty hospitals as context, and public signals</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>04 Multiples and benchmark</t>
+          <t>05 Deal A</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Valuation and leverage multiples over time, the benchmark of eleven operators, wellness clinics and emergency and specialty hospitals as context, and public signals</t>
+          <t>The thesis, our readings, the evidence behind them, sensitivities and information requests</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>05 Deal A</t>
+          <t>06 Deal B</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>The thesis, our readings, the evidence behind them, sensitivities and information requests</t>
+          <t>The thesis, our readings, Deal B Wellness Clinics on its own, sensitivities and information requests</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>06 Deal B</t>
+          <t>07 Deal C</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>The thesis, our readings, Deal B Wellness Clinics on its own, sensitivities and information requests</t>
+          <t>The thesis, our readings, the evidence behind them, sensitivities and information requests</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>07 Deal C</t>
+          <t>08 Financing observations</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>The thesis, our readings, the evidence behind them, sensitivities and information requests</t>
+          <t>The proposed financings of the three deals, as observations for ABC Private Credit's own underwriting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>08 Financing observations</t>
+          <t>09 Assumptions and method</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>The proposed financings of the three deals, as observations for ABC Private Credit's own underwriting</t>
+          <t>The register, method, definitions, sources, evidence index, computation notes and limits, and the supporting evidence moved from the main body, part by part</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>09 Assumptions and method</t>
+          <t>10 FAQ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>The register, method, definitions, sources, evidence index, computation notes and limits, and the supporting evidence moved from the main body, part by part</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>10 FAQ</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Answers to the questions a credit committee is likely to ask</t>
         </is>
@@ -53240,603 +50954,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Part 02 — About CreditSwan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Part 02 — About CreditSwan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Prepared for</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>ABC Private Credit, credit team</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>258 source files · 366 public figures</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Every number traced to source</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A · Deal clock</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>IOI – LOI</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Diligence (3-day median)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Hold &amp; exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>The pack</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Pack · terms · covenants</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Pack · terms · covenants</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Operator 35</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Initial · go / no-go</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Initial · go / no-go</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Weekly board</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Weekly board</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>B · Deal Diligence</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>What the pack answers</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>QoE</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Commercial DD</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>CreditSwan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Accounting policy &amp; adjusted EBITDA</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Market size &amp; positioning</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Revenue &amp; cost reconciled to the bank, transaction level</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Gross-to-net &amp; promo dependence</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>CAC &amp; channel economics</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Cohort &amp; repeat-purchase decay</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Customer &amp; channel concentration</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Share of search, foot traffic &amp; syndicated retail</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Recommendation, covenants and the source trail, committee-ready</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Not covered</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>What it reads</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Trial balance</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Surveys &amp; expert calls</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Raw system exports + hundreds of outside sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>B · Deal Diligence</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Evidence 01 · From the data room, file by file</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Evidence 02 · Hundreds of outside data points</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>The folders ABC Private Credit supplied — clinic-level P&amp;Ls, KPI datapacks, QoE reports, audited statements and lender and sponsor models — with every number registered to its file and page.</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Public filings, price, wage and demand statistics, and industry reports, tested against every commercial claim so the numbers carry context, not just history; and company pages, clinic lists, census trade areas and employer and complaint sites, read on 30 September 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>258 source files · 13 folders · Clinic-level P&amp;Ls · KPI datapacks · QoE reports · Audited statements · Lender models · Sponsor models</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>134 public series · 366 public figures from 149 public sources · SEC EDGAR · BLS CPI · PPI · ECI · BEA NIPA · FRED · industry pet-ownership survey · Census MRTS · Census ACS trade areas · pet insurance industry data · animal health market data · Company clinic lists and pages · Industry reports, claim by claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>C · Operator 35</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>For lenders and sponsors</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>For CEOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Covenant headroom and early warning on every portfolio company, read from the same systems the underwriting used, with a diagnosis attached and a named owner before anything changes.</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>The same board on your own business. What moved this week, why, and what to change, before your lender or your board asks the question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>D · How it is built</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>01 Capture</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>02 Compute</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>03 Deliver</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Raw exports and live APIs from hundreds of systems. Immutable snapshots, every field fingerprinted to its source file.</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Deterministic Python + SQL. Private-VPC models suggest mappings and analysts approve them. No LLM generates a figure.</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Diligence packs and weekly diagnostics, with lineage attached to every number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>D · How it is built</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Monitors</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Median clock</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Source systems</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>LLM-generated figures</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>20+</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>3 days</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>86s</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Read every week after close</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Data access to committee-ready pack</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>No engagement waits on a connector</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Models map; analysts approve</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -55805,21 +52922,21 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A68:J68"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A68:J68"/>
     <mergeCell ref="A51:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -59087,7 +56204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60091,7 +57208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62069,7 +59186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62916,9 +60033,9 @@
   <mergeCells count="13">
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A18:F18"/>
@@ -62930,4 +60047,2258 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Part 08 — Financing observations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Assumptions used in Part 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Value used</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Every multiple states its earnings measure and the debt it counts</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Leverage from first-lien funded debt up to all debt with leases and supplier finance; multiples marked standalone or synergised</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA is kept on named levels</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Reported, adjusted, pro forma, run-rate, underwriting and cash EBITDA (pro forma less "one-time" costs that recur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>A-F11</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Operating case on the recapitalisation model</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>The model of 29 September as it stands: scenario 3, downside on, closure scenario off</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>A-F12</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Closure cash and fees on the recapitalisation model</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>$21.79m over 42.1 months from April 2027 and $4.3m of fees in the June 2027 quarter, funded on the revolver</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>A-F13</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Net closure benefit in the lead case</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>$2.9m a year from April 2027 (clinic EBITDA including co-op, operating leases run to term)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>A-F10</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Refinancing need</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Bank debt at September 2030 less cash above a $13m reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.01 — On the evidence to October 2026, three financing readings are contradicted in whole or in part and one rests on missing terms; at Deal A the recapitalisation model repays supplier finance at close and liquidity is the tighter test, funding at Deal B is tested before the leverage covenant, and at Deal C Option Two's fixed-charge cover on cash EBITDA is below 1.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Our reading on the financing component of each thesis (M5, MS6, ST4 Option Two and Option One), with the depth of the evidence and what would change it; audited figures to FY26, models and term documents of September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ABC Private Credit asked</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Our answer in brief</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Evidence behind it</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>What would change it</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Deal A: its scale and diversity make it compelling at a low leverage multiple (M5)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted as "resilient at low leverage"; partially supported as a sale-bridged loan. On the recapitalisation model of 29 September the $254m of funded debt is 3.51x gross first lien on the model's LTM 2Q27F EBITDA of $67.2m, and supplier finance is repaid at close; the leverage covenant peaks at 5.68x against 6.35x. With the company's closure cash and a $2.9m net closure benefit, minimum liquidity is $33.3m against a $21m minimum (March 2029), and a 4.05% EBITDA shortfall takes it below; the model's own fixed-charge cover is 0.76–1.03x from March 2027 to FY31 (Part 08 section B).</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Audited FY26 accounts and the June 2026 quarter (actual); the recapitalisation model of 29 September (projected), with a CreditSwan overlay for the company's closure cash and three closure-benefit cases; the 21 September term sheet, the only term sheet in the files.</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>July–September 2026 actuals; a term sheet on the model's structure, with its fixed-charge cover and liquidity tests; the closure cash budget and lease-exit plan; a third-party valuation of the owned real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Deal B: a low-levered, high-priced deal with upside (MS6)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted — on trailing leverage, cover and funding. On ABC Private Credit's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>ABC Private Credit's response to the borrower's financing grid (19 September 2026) and the borrower's and ABC Private Credit's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>The agreed closing EBITDA and the measure it is struck on; cash at close; executed HoldCo terms; a sources-and-uses for the acquisition batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Deal C: the leverage requested is 5.3x (ST4, Option Two)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted. The $204.3m first lien is 5.96x gross on ABC Private Credit's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ABC Private Credit's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>The Accounting Firm 1 quality-of-earnings report; the affiliate-bonus agreements; August–September 2026 same-store EBITDA against the 1.57% threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Deal C: the leverage requested is 5.3x (ST4, Option One)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on ABC Private Credit's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>As for Option Two; the sponsor instrument's coupon, maturity, ranking and cash-pay terms are not in the documents supplied.</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>The sponsor instrument's coupon, maturity, ranking and cash-pay terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Source: Part 08 section B, Part 08 section C and Part 08 section D · Basis: Leverage on reported (A) and underwriting (P or PF) earnings as named; liquidity and refinancing from models (P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.02 — Readings on the three proposed financings (to October 2026): Deal A's $254m on the recapitalisation model is 3.51x first lien and peaks at 5.68x on the lease-adjusted covenant, Deal B's stack reads 7.59x, and Deal C's 5.96x first lien sits above every 2025–26 same-rung print</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Reading label, basis, what holds, what does not and what would change it, for the financing component of each deal; leverage x, amounts $m; evidence supplied to 1 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Thesis component</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Our reading on the evidence supplied to date</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>What holds</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>What does not</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>What would change it</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Deal A</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>M5 · Low-leverage financing is resilient</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted as "resilient at low leverage"; partially supported as a sale-bridged loan</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>On the recapitalisation model of 29 September: $254m of funded debt, 3.51x gross and 2.80x net first lien on LTM 2Q27F EBITDA of $67.2m (P); adjusted gross debt ÷ EBITDAR peaks at 5.68x against 6.35x; with the workbook's closure cash and a $2.9m net benefit minimum liquidity is $33.3m against $21m, breached at a 4.05% EBITDA shortfall; the model's fixed-charge cover is 0.76–1.03x from March 2027 to FY31; at 4.3x the lead-case need of $257.8m is covered on reported LTM EBITDA (+$34.2m) and not on FY26 (−$8.6m) or on the model's LTM 2Q27F (−$33.9m) (Part 08 section B)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; ABC Private Credit's Diligence &amp; Structure Update states that the sale process has been launched</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>A 4.05% EBITDA shortfall takes liquidity below $21m in the lead case, and 1.6% with no closure benefit; closure cash paid inside four quarters takes it to $19.5m ($15.1m with no benefit); the model's fixed-charge cover is below 1.0x from March 2027 to March 2028; at maturity the debt does not refinance at 4.3x on FY26 or on the model's own closing EBITDA</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>July–September 2026 actuals; a term sheet on the model's structure, with the fixed-charge cover and liquidity tests; the closure cash budget and lease-exit plan; a third-party valuation of the owned real estate, including the 26 sale-leaseback sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>MS6 · Low leverage, pricing and upside compensate</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted — on trailing leverage, cover and funding</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m (term loan $55m); fixed-charge cover 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on ABC Private Credit's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>The agreed closing EBITDA and rung; cash at close; executed HoldCo terms; a sources-and-uses for the batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ST4 · 5.3x leverage is supportable — Option Two</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Contradicted</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>5.96x gross first lien on ABC Private Credit's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Cover computes at 0.96x on ABC Private Credit's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>The Accounting Firm 1 QoE; the affiliate-bonus agreements; August–September same-store EBITDA against the 1.57% threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>ST4 · 5.3x leverage is supportable — Option One</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence — sponsor-instrument terms missing</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>5.30x gross first lien, outside the 3.81–5.10x band; 5.76x net incl. sponsor debt; debt service untestable without the sponsor terms; the refinancing result reverses with a 17% cash coupon (senior tranche) or a drawn delayed-draw loan (total debt) (Part 08 section D)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Cover computes at 1.00x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>The 5.30x gross first lien sits above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); the $21m sponsor instrument's coupon, maturity, ranking and cash-pay terms are not in the files; a 17% cash coupon on it reverses the senior result, and the delayed-draw loan drawn at the audited deal-cost rate leaves total debt short</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>The sponsor instrument's coupon, maturity, ranking and cash-pay terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Source: Leverage from first-lien funded debt to all debt with leases and supply-chain finance, and cash EBITDA after recurring deal costs, are defined in Part 09 section C · Basis: Figures as set out, with their references and bases (A, PF, P), in Part 08 section B, Part 08 section C and Part 08 section D</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in ABC Private Credit's model of September</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Main terms of the LW draft term sheet of 21 September 2026 (with ABC Private Credit's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>LW draft term sheet, 21 September 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Recapitalisation model v06, 29 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Commitments</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>$336m: $111m super-senior revolver, $111m term loan, $111m delayed-draw term loan</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>$336m: $111m revolver, $218m term loan; no delayed-draw loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Drawn at close</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Revolver $44m deemed drawn; term loan $111m; ABC Private Credit's model v24: $152m of bank debt</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Revolver $44m (minimum draw $44m); term loan $218m; total debt $254.5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Supplier finance</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Unwound over 15 months through the delayed-draw loan, subject to a 5.15x draw test</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>$145m repaid at close; the remaining Lender 6 line winds down over six months</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Pricing and fees</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>S+5.26% term facilities; S+3.26% revolver, 21bp grid</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>S+5.26% term loan, 1% amortisation, 2% fee; S+3.26% revolver, 0.44% unused fee, 2% fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Sweeps</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>67% of excess cash flow</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>67% of excess cash flow; 100% of asset-sale proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Leverage at close</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1.9x first lien on ABC Private Credit's $71.7m (LTM Sep-26, including a forecast quarter)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>3.51x gross, 2.80x net on LTM 2Q27F EBITDA of $64.45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Leverage covenant</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Lease-adjusted net leverage, 6.35x stepping to 5.81x</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Adjusted gross debt ÷ EBITDAR against a flat 6.35x on the Covenants tab (step-downs listed elsewhere in the model); peak 5.68x, March 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Minimum liquidity</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>$21.5m of average daily liquidity, tested quarterly</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>$21m input not referenced by any formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Fixed-charge cover</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>No maintenance test</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Labelled "≥1.08"; computes 0.76–1.03x from March 2027 to FY31</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Second-round closures</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>ABC Private Credit's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Closure scenario off: no benefit and no closure cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>December 2026 dividend</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>$7.4m permitted outside the payment conditions</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>$7.41m paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Close and maturity</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Calendar dates, not mapped to Deal A's fiscal quarters</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Close 14 October 2026; maturity 30 September 2030 on the drivers tab, 31 October 2030 on the capital-structure tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); ABC Private Credit Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Proposed debt at close (30 September 2026) ÷ EBITDA, x, gross, for the $55m and $52m term loans on six EBITDA denominators, with the peer comparison on the same rung</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Denominator (rung; basis; row block)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>TL $55m: LV1 / LV3 / LV4</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>TL $52m: LV1 / LV3 / LV4</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Peer comparison on the same rung</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>E1 LTM Jul-26 $1.22m (A; DLB-9442 / 8012)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>39.7x / 47.2x / 74.9x</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>38.2x / 44.5x / 72.4x</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Operator 6 LV1 on E1 as owned 16.59x (OP6-0034); Deal B above</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>E2 post-audit LTM Jul-26 $8.51m (PF; DLB-9424 / 8196)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>5.58x / 6.55x / 10.43x</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>5.53x / 6.17x / 10.16x</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>No peer prints first-lien leverage on E2 alone; not placed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>E5 ABC Private Credit LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>4.08x / 4.91x / 7.59x</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>3.91x / 4.53x / 7.77x</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5, 2025–26 same-rung set: Operator 7 2.25x (P), Operator 6 3.81x (PF closed), Operator 3 4.70x (P), Operator 4 5.10x on Lender 1's E5 (PF) (OP7-1181; OP6-0031; OP3-1326; OP4-1442): inside. LV4: Operator 8 5.4–5.68x net (OP8-2819/2452/2367), Operator 1 6.0–7.2x net (OP1-10738/10730): above all</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>E4 post-audit LTM Jul-26 $13.79m (PF; DLB-9406 / 8010)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>3.41x / 3.94x / 6.38x</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>3.24x / 3.68x / 6.13x</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Operator 6 LV1 on buy-side QoE pro forma (E3) 4.84x (OP6-0032): below by 1.6–1.8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>E4 borrower LTM Sep-26E $14.77m (P; DLB-9370 / 8001)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>3.28x / 3.71x / 5.99x</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>2.95x / 3.44x / 5.58x</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on financing EBITDA (E4/E5, the Exhibit 4.09 convention): 2025–26 same-rung set 2.25–5.10x inside; closed first-lien band since 2014 3.81–4.27x below</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>E5 borrower $16.1m incl. acquisitions (P; DLB-9388 / 8163)</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2.84x / 3.30x / 5.39x</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>2.80x / 3.14x / 5.17x</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>as above: inside</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="39" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Source: DLB-026 (ABC Private Credit response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on ABC Private Credit's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>First-lien funded debt ÷ EBITDA, x, gross and net, by print and rung; Deal C at the September 2026 close, peers 2014 to 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Rung and basis</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Locator</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Deal C Option Two (P)</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5 $29.4m, LTM Sep-26E</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>5.96x</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>5.92x</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>DLC-4725/4726</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Deal C Option One (P)</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>5.30x</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>5.10x</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>DLC-4872/4873</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Deal C Option One incl. $21m sponsor debt (P)</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>LV4 on E5</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>5.96x</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>5.76x</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>DLC-4878/4879</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Deal C FY25 legacy facilities (A)</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on D3 E1 / E2 / E3 / E3-E4 model</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>24.9x / 6.6x / 5.4x / 4.5x</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>22.5x / 6.2x / 5.1x / 4.3x</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>DLC-4459/4460; 3891/4502; 3977/4516; 3924/4544</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Operator 6, Jul-26 close (PF)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>3.81x</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>OP6-0031</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Operator 3, Dec-25 proposal (P)</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>4.70x</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>OP3-1326</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Operator 4, Mar-26 (PF)</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on Lender 1 E5</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>5.10x</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>OP4-1442</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Operator 7, 2026 proposal (P)</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E5 $8.8m</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>2.25x</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>1.97x</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>OP7-1181/1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Closed core prints, 2014–26</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on financing EBITDA (E4/E5)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>median 4.3x (3.81–5.97x)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>notes C-75 and C-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Operator 2 Sponsor 1 LBO, Sep-21 (PF)</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>LV1 on E4</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>5.97x</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>6.05x</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>P5-S001; OP2-3732</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Operator 1, REOPEN21 / INFL22-23 (PF)</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>LV4 net on financing EBITDA</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>7.19x / 5.98x</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>OP1-10730; OP1-10738</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Deal A, Operator 9, Operator 4 (A)</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>LV1 gross on D3 E1: Deal A FY26 / Operator 9 FY Sep-25 / Operator 4 FY24</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>0.62x / 6.32x / 8.60x</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DLA-0472; OP4-1464; OP4-1394</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Source: rows as listed; Exhibit 9.75. Proposals (P) and closed prints are shown separately and not pooled · Basis: Deal C options P; legacy facilities A; peers PF, P or A as marked</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.16 — On the recapitalisation model the closure benefit's definition moves the EBITDA shortfall that takes Deal A's liquidity below $21m from 1.6% to 11.9%, and paying the closure cash inside four quarters takes the minimum below $21m; the leverage covenant is never the first signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Sensitivities that bear on the Deal A financing, set against observed ranges; CreditSwan overlay on the recapitalisation model v06 (29 September 2026); minimum quarter-end liquidity net of letters of credit, $m; refinancing at 30 September 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Result on the recapitalisation model</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Observed range (source)</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Reading on the observed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Closure benefit</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>No benefit $27.1m (below $21m at a 1.6% shortfall); $2.9m net benefit $33.3m (4.05%); management's $12m $37.0m (11.9%)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Second-round cases of −$11.8m to +$20.4m a year, by measure of the benefit and lease exits (Part 05 section D)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Among the cases with closure cash paid as the leases run, the definition of the benefit moves the threshold from 1.6% to 11.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Timing of closure cash</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Over the remaining lease terms: $27.1m without benefit, $33.3m with it; inside four quarters: $15.1m and $19.5m</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Workbook costs run to lease end, 42.1 months on average; 30 of 109 leases end within 21 months (FY27 Closing Clinics Financial Analysis)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Paid as the leases run, the minimum clears $21m; paid inside four quarters, for example to buy out leases, it does not</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA shortfall</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Lead case below $21m at 4.05%; with no benefit and a 9% shortfall, liquidity below zero from December 2029 (−$14.1m by March 2031) and the leverage ratio peaks at 5.58x</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Deal A's own annual declines in reported EBITDA of 7.7–23.5% (FY23–FY26) and −34% year on year in company EBITDA in the first quarter of FY27 (Deal A 10-K FY23–FY26; bank model row 181)</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>The liquidity threshold lies inside Deal A's observed declines; the leverage covenant does not give the first signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Leverage covenant level</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Peak 5.68x (lead) and 5.58x (9% shortfall) against a flat 6.35x; 0.67x of margin against the 6.13x step from June 2027 in the shortfall case</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>The model lists step-downs from 6.35x to 5.81x (Draw Schedule Summary row 101) but tests a flat 6.35x</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Which schedule applies is a point to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Refinancing multiple</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Lead-case need $257.8m at 30 September 2030</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Closed first-lien prints 3.81–4.27x (Operator 2's 2021 buyout at 5.97x aside), median 4.3x (Part 04 section B)</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>At 4.3x: +$34.2m on reported LTM EBITDA, −$8.6m on FY26, −$33.9m on the model's LTM 2Q27F; at 3.81x every actual rung falls short</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Sale-leaseback</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Proceeds of $44.4m on the term loan take gross leverage on LTM 2Q27F EBITDA after the new rent from 3.51x to 3.06x</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>26 sites; 14 with a site loss in FY26; rent cover 1.23x on $3.44m of year-one rent rising 2.2% a year (Project Charlie I-Chart)</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Lowers funded debt, adds rent, and takes 26 sites out of the real estate behind recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="39" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Source: Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026); FY27 Closing Clinics Financial Analysis (DLA-027); Project Charlie I-Chart (DLA-029); notes C-V2-3 to C-V2-5; observed ranges as cited in each row · Basis: P for the model results [I]; A for the observed ranges unless marked · Assumption: A-F11, A-F12, A-F13, A-F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.17 — Deal B needs EBITDA above both current measures to refinance in December 2030 and its batch is $8.8–11.8m short; Deal C's Option Two needs at least 1.57% a year of EBITDA growth against +1.0% and −5.8% observed</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Financing sensitivities of the Deal B and Deal C proposals: ABC Private Credit's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>ABC Private Credit's case</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>What the evidence shows</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Value tested</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Effect on the financing reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA rung for leverage</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>2025–26 same-rung first-lien prints 2.25–5.10x (Operator 7 and Operator 3 proposals, Operator 6 closed, Operator 4 on Lender 1's E5); closed first-lien band since 2014 3.81–4.27x on financing EBITDA, Operator 2's 2021 5.97x aside; peer LV4 prints 5.4–7.2x (OP7-1181; OP6-0031; OP3-1326; OP4-1442; OP8-2819/2367; OP1-10730/10738)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>First lien 2.84x on the borrower's $16.1m to 5.58x on post-audit $8.51m; with the HoldCo 5.39x to 10.43x (DLB-9388..9391; DLB-9424..9427)</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on ABC Private Credit's EBITDA (Part 08 section C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Fixed-charge cover</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>FCCR_CD on ABC Private Credit's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Peer prints 0.7–1.6x on mixed definitions; association only (note C-80)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (ABC Private Credit's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Cover is about 1x on the borrower's EBITDA and below 1x on ABC Private Credit's; the peer prints are on different definitions, so no position is taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>HoldCo accretion, EBITDA flat for twelve months</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>HoldCo note of $36.9m at 15% PIK (DLB-5668)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Contractual accretion to $44.0m by September 2027 (DLB-9111); peer LV4 prints 5.4–7.2x</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Total leverage 7.85–8.25x on ABC Private Credit's $11.16m and 6.00–6.35x on $14.77m</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>With EBITDA flat, total leverage on ABC Private Credit's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Refinancing at December 2030</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Senior debt of $79–82m and the HoldCo note at $73.3m at maturity (DLB-6246)</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Closed first-lien band 3.81–4.27x, median 4.3x (Exhibit 4.09); peer LV4 5.4–7.2x</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA of $16.1–16.6m refinances the term loan and delayed-draw loan at 4.3x; $18.6–24.6m refinances them with the HoldCo at 5.4–7.2x</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Both thresholds sit above today's $11.16m on ABC Private Credit's measure and $13.79m post-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Deal B</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Funding of the near-term batch</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (ABC Private Credit model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>The 23-unit batch needs a $47.5m delayed-draw draw (DLB-6069..6077)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>Residual shortfall $8.8m or $11.8m after the $4.3m liquidity floor (C-FIN-5)</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>On either model's closing cash the committed facilities leave the batch $8.8–11.8m short</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA rung for leverage</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Option Two's $204.3m first lien at 5.96x gross on ABC Private Credit's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>2025–26 same-rung prints 3.81–5.10x at Operator 6, Operator 3 and Operator 4, with Operator 7 2.25x proposal below; closed first-lien median 4.3x since 2014 (OP6-0031; OP3-1326; OP4-1442; OP7-1181; P5-S001)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>Above every 2025–26 same-rung print and above the 4.3x closed median on every EBITDA measure in the files; among closed first-lien prints since 2014 only Operator 2's 2021 buyout (5.97x) is higher</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Fixed-charge cover</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>ABC Private Credit's coverage method on its cash EBITDA</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Cash breakeven EBITDA for Option Two $26.0m (DLC-4983)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Option Two 0.76x ($23.2m), 0.77x ($24.9m), 0.96x ($29.4m), 1.08x ($32.3m), 0.22x ($8.6m); Option One, term loan only at S+451: 1.00x ($24.9m), 1.23x ($29.4m), 1.37x ($32.3m) (DLC-4947..4982)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Option Two covers its fixed charges only on EBITDA that includes forecast months</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Organic EBITDA growth to maturity</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Option Two on ABC Private Credit's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Same-store clinic EBITDA +1.0% for CY2025 and −5.8% for LTM July 2026 (DLC-0987; DLC-0996)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Gap at the 4.3x median: $23.0m flat, $7.5m at +1.0%, $101m at −5.8%; clears from 1.57% a year on $29.4m and 5.36% on $24.9m</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Refinancing needs growth above what Deal C's clinics delivered in the latest two periods</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Refinancing multiple</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>4.3x median of closed first-lien prints (notes C-75 and C-76)</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>3.81x (Operator 6, closed) to 5.10x (Operator 4 on E5); 3.38x as a stress</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Flat $29.4m clears only at 5.18x; gap of $53.0m at 3.38x</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>On flat earnings Option Two clears only at the top of the observed band</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>DDTL drawn</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>$70m DDTL for acquisitions, left undrawn on the no-acquisition path</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Deal costs 13.2% of price excluding affiliate bonuses ((DLC-0009 − DLC-0199) ÷ total consideration) and 31.2% on the audited rate (DLC-0009 ÷ total consideration of $32.8m, 2025 Audit Note 3, p.17)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>DDTL drawn at close, acquired EBITDA leverage-neutral (assumed)</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Option Two's gap at 4.3x on flat $29.4m widens from $23.0m to $35.7–51.5m; Option One's total debt misses by $8.0m at the audited rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Deal C</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Sponsor instrument on cash pay</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Option One's $21m sponsor instrument carried at face with no cash coupon; its terms are not in the files [U]</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>No coupon, maturity, ranking or cash-pay term in the files</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Cash coupon of 12% or 17% (assumed)</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Option One's senior gap at 4.3x moves from −$23.9m to −$8.1m (10%) and +$2.3m (17%); its total gap to $13.4–23.4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="39" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Source: Rows as cited in each cell; the underlying tables are Exhibit 8.10, Exhibit 9.162, Exhibit 9.164, Exhibit 9.165, Exhibit 9.166 and Exhibit 8.14; notes C-80, C-90 and C-FIN-5 · Basis: P for the proposed structures and every forward result; A or PF for the observed ranges as marked. All results [I] · Assumption: Growth rates other than Deal C's observed +1.0% and −5.8%, the 3.38x stress, the drawn DDTL and the sponsor coupons of 12% and 17% are assumed parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit 8.19 — Read against the recapitalisation model of 29 September, three of the fifteen observations fall away with the delayed-draw loan, two largely or partly fall away with supplier finance repaid at close, and fixed-charge cover and the untested liquidity minimum become the points to settle</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Each observation on the LW draft term sheet (21 September 2026), with what the recapitalisation model v06 (29 September 2026) shows and its status; points to confirm in the model added</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Observation on the term sheet of 21 September</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>On the recapitalisation model of 29 September</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Leverage-ratio denominator: EBITDAR reading; stock compensation</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Computes on EBITDAR and adds back stock compensation ($6.2m LTM at March 2027, Covenants!J86); the term-sheet wording is still to settle</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Point to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Covenant levels well above the modelled path (4.53x peak on ABC Private Credit's model v24)</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Peak 5.68x against 6.35x (1.0x of room); the Covenants tab shows a flat 6.35x, the Draw Schedule Summary step-downs to 5.81x (row 101)</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Holds, with less room</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Delayed-draw condition tested at each draw</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>No delayed-draw loan; supplier finance repaid at close</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Falls away</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Revolver cap while the delayed-draw loan is available</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>No delayed-draw loan</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Falls away</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Letters of credit of at least $25.5m</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>The model carries $26m (Scenario Drivers!G23)</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Point to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Qualified Cash and control agreements</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Not addressed in the model</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>December 2026 dividend outside the payment conditions; fixed-charge payment condition; run-rate add-backs</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>$7.41m paid in December 2026 (Draw Schedule Summary!J39); fixed-charge cover 0.77x at March 2027</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>EBITDAR clauses; disposal gains; closure-cash sub-cap</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per ABC Private Credit verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Point to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Calendar against fiscal dates</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Close 14 October 2026; maturity 30 September 2030 (Scenario Drivers!G77) against 31 October 2030 (PF Cap Structure!E11, E13)</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Point to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Supplier finance inside funded debt</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>$145m repaid at close; the remaining Lender 6 line winds down over six months (Scenario Drivers!G36)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Largely falls away</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Excess-cash-flow treatment of supplier-finance payments and delayed-draw proceeds</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>67% excess-cash sweep and 100% asset-sale sweep</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Partly falls away</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Prepayment premium on closure-programme proceeds</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged; now also bears on the sale-leaseback ($44.4–46.9m at Real Estate Advisor 1 values) under the 100% asset-sale sweep</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Delayed-draw amortisation; debt carried in ABC Private Credit's model v24</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>No delayed-draw loan</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Falls away</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Conditions precedent; no mortgage provision</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged; the sale-leaseback would take 26 owned sites out of the real estate behind recovery</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>No fixed-charge cover maintenance test</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Labelled "≥1.08"; the model's own path is 0.93x at December 2026 and 0.76–1.03x from March 2027 to FY31, below that level in every period were it a covenant</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Point to settle</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Points to confirm in the model</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>The $21m minimum liquidity input (Scenario Drivers!G31) is referenced by no formula; the first downside input (G32, $3.0m) is applied as $0.8m in the monthly P&amp;L (row 127), the other two ($2.6m, $5.9m) agree; Covenants!G85:I85 hard-code LTM EBITDA of $79.5m / $75.9m / $69.8m against the model's own $64.5m at December 2026 (Draw Schedule Summary!J106); the closure scenario is off; no sale-leaseback line</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Points to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="39" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026), cells as cited in each row; the fifteen observations on the term sheet in Part 09 section O · Basis: Model terms and results as the model computes them [F]; projected (P). Statuses are our reading [I]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A76:D76"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
+++ b/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Alpha - FY27 Clinic Closure Data, Summary!J43, J33, B49; fees ABC Private Credit Deal A Model v24, MODEL OUTPUT!F21; note C-FIN-4</t>
+          <t>Alpha - FY27 Clinic Closure Data, Summary!J43, J33, B49; fees Ares Credit Group Deal A Model v24, MODEL OUTPUT!F21; note C-FIN-4</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Row 152 is the bank model's principal line; ABC Private Credit's model nets the interest out (MODEL OUTPUT!D30, D171)</t>
+          <t>Row 152 is the bank model's principal line; Ares Credit Group's model nets the interest out (MODEL OUTPUT!D30, D171)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 as it stands: EBITDA, $12m closure benefit from April 2027, capex, working capital, taxes, $177.7m of supplier-finance payments</t>
+          <t>Ares Credit Group's model v24 as it stands: EBITDA, $12m closure benefit from April 2027, capex, working capital, taxes, $177.7m of supplier-finance payments</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28</t>
+          <t>Ares Credit Group Deal A Model v24, MODEL OUTPUT rows 13 to 28</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>EBITDA 9% below ABC Private Credit's model in every period; no closure benefit</t>
+          <t>EBITDA 9% below Ares Credit Group's model in every period; no closure benefit</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>$13m is the minimum cash in ABC Private Credit's model (MODEL OUTPUT!F159:L159); note C-FIN-3</t>
+          <t>$13m is the minimum cash in Ares Credit Group's model (MODEL OUTPUT!F159:L159); note C-FIN-3</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>FY27 Closing Clinics Financial Analysis, Summary!J43; fees ABC Private Credit Deal A Model v24, MODEL OUTPUT!F21; note C-V2-4</t>
+          <t>FY27 Closing Clinics Financial Analysis, Summary!J43; fees Ares Credit Group Deal A Model v24, MODEL OUTPUT!F21; note C-V2-4</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit hypothesis or ABC Private Credit model output</t>
+          <t>Ares Credit Group hypothesis or Ares Credit Group model output</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.11 — Twelve forms of reference, each resolving in a named section of this document, in a document ABC Private Credit holds or at a public address with the date it was read</t>
+          <t>Exhibit 9.11 — Twelve forms of reference, each resolving in a named section of this document, in a document Ares Credit Group holds or at a public address with the date it was read</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>A document ABC Private Credit supplied, by source ID or short name, and the page</t>
+          <t>A document Ares Credit Group supplied, by source ID or short name, and the page</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>A workbook ABC Private Credit supplied, the tab and the cell or range</t>
+          <t>A workbook Ares Credit Group supplied, the tab and the cell or range</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Deal A (including the ABC Private Credit model)</t>
+          <t>Deal A (including the Ares Credit Group model)</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.14 — Each supplied document is cited by one ID that resolves to its file name as ABC Private Credit holds it and its date; Deal A's public filings are one entry</t>
+          <t>Exhibit 9.14 — Each supplied document is cited by one ID that resolves to its file name as Ares Credit Group holds it and its date; Deal A's public filings are one entry</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>File name as ABC Private Credit holds it</t>
+          <t>File name as Ares Credit Group holds it</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -4407,14 +4407,14 @@
     <row r="207" ht="30" customHeight="1">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.15 — Six source files received on 1 October 2026 were read: four on Deal A's financing, second round and current trading, and Deal B's and DBW's answers to ABC Private Credit's diligence questions</t>
+          <t>Exhibit 9.15 — Six source files received on 1 October 2026 were read: four on Deal A's financing, second round and current trading, and Deal B's and DBW's answers to Ares Credit Group's diligence questions</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>Registry ID, short name, file name as ABC Private Credit holds it with its folder, document date, what the document is and the evidence tag its figures carry; the other 49 files received that day are copies of files already held</t>
+          <t>Registry ID, short name, file name as Ares Credit Group holds it with its folder, document date, what the document is and the evidence tag its figures carry; the other 49 files received that day are copies of files already held</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>File as ABC Private Credit holds it</t>
+          <t>File as Ares Credit Group holds it</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>DLB ABC Private Credit Diligence Responses</t>
+          <t>DLB Ares Credit Group Diligence Responses</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>NEW FILES OCT 1/Deal B/DLB ABC Private Credit Diligence [file]</t>
+          <t>NEW FILES OCT 1/Deal B/DLB Ares Credit Group Diligence [file]</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>DBW ABC Private Credit Diligence Responses</t>
+          <t>DBW Ares Credit Group Diligence Responses</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>NEW FILES OCT 1/Deal B/DBW ABC Private Credit Diligence [file]</t>
+          <t>NEW FILES OCT 1/Deal B/DBW Ares Credit Group Diligence [file]</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>Rows read from ABC Private Credit's investment memos (IDs P5-S)</t>
+          <t>Rows read from Ares Credit Group's investment memos (IDs P5-S)</t>
         </is>
       </c>
       <c r="B463" s="10" t="n">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="D522" s="7" t="inlineStr">
         <is>
-          <t>DLB-031 internal QoE; DLB-023; DLB-030; DLB-014/015/016; DLB-021; DD answers received in part on 1 October 2026 (DLB ABC Private Credit Diligence Responses, DLB-033)</t>
+          <t>DLB-031 internal QoE; DLB-023; DLB-030; DLB-014/015/016; DLB-021; DD answers received in part on 1 October 2026 (DLB Ares Credit Group Diligence Responses, DLB-033)</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="D532" s="7" t="inlineStr">
         <is>
-          <t>Compliance certificates in OP1-048, OP4-005, OP8-014; 2012 ABC Private Credit memo</t>
+          <t>Compliance certificates in OP1-048, OP4-005, OP8-014; 2012 Ares Credit Group memo</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D544" s="7" t="inlineStr">
         <is>
-          <t>10-K/10-Q, clinic-level EBITDA, KPI files, ABC Private Credit IC and term sheet</t>
+          <t>10-K/10-Q, clinic-level EBITDA, KPI files, Ares Credit Group IC and term sheet</t>
         </is>
       </c>
       <c r="E544" s="7" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="D555" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit memo (CIM/QoE figures reproduced)</t>
+          <t>Ares Credit Group memo (CIM/QoE figures reproduced)</t>
         </is>
       </c>
       <c r="E555" s="7" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="F557" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA / FCCR</t>
+          <t>Ares Credit Group cash EBITDA / FCCR</t>
         </is>
       </c>
       <c r="G557" s="7" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="B625" s="7" t="inlineStr">
         <is>
-          <t>Comp sales Apr-20, revenue, as stated in ABC Private Credit's February 2021 Operator 1 transaction memo (OP1-033 p.31)</t>
+          <t>Comp sales Apr-20, revenue, as stated in Ares Credit Group's February 2021 Operator 1 transaction memo (OP1-033 p.31)</t>
         </is>
       </c>
       <c r="C625" s="15" t="n">
@@ -22482,7 +22482,7 @@
     <row r="817">
       <c r="A817" s="7" t="inlineStr">
         <is>
-          <t>Operator 3, ABC Private Credit chart</t>
+          <t>Operator 3, Ares Credit Group chart</t>
         </is>
       </c>
       <c r="B817" s="7" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>+3.0 / +2.3 / +0.3% ABC Private Credit-presented (OP1-048)</t>
+          <t>+3.0 / +2.3 / +0.3% Ares Credit Group-presented (OP1-048)</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>+1.9% ABC Private Credit-presented (+1.8% OP4-005 panel)</t>
+          <t>+1.9% Ares Credit Group-presented (+1.8% OP4-005 panel)</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>~5.8% ABC Private Credit memo (no definition)</t>
+          <t>~5.8% Ares Credit Group memo (no definition)</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
@@ -25805,7 +25805,7 @@
       </c>
       <c r="E944" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit "cash" 23.2 as printed, 24.9 corrected for a non-cash impairment (LTM)</t>
+          <t>Ares Credit Group "cash" 23.2 as printed, 24.9 corrected for a non-cash impairment (LTM)</t>
         </is>
       </c>
       <c r="F944" s="7" t="inlineStr">
@@ -25822,7 +25822,7 @@
     <row r="945" ht="91" customHeight="1">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>Source: note C-61; Deal A rows from the 10-K public series DLA_EBITDA_E1 and DLA_EBITDA_ADJ_PUB; Deal C rows DLC-0019, DLC-4434 (E1), DLC-4426, DLC-4430 (E3), DLC-4107, DLC-4443 (ABC Private Credit cash EBITDA). ADJ_SHARE = (top rung − E1) ÷ top rung; E6 = D3 cash EBITDA (top rung less recurring cash "one-time" items). Basis: E1 A; E2/E3/E6 PF; Deal A E2m is a reconstruction from company-published non-GAAP items; Operator 2 E1 is compliance-certificate basis [M]. Clinic base ALL (consolidated). The E6/top median of 0.84 is across the eleven Operator 4, Operator 8, Operator 6 and Operator 3 readings. Operator 8's E6 is built from its as-owned adjusted EBITDA (E2m, OP8-1880) and is set against that rung; its E3 (OP8-2409) is fully pro forma for acquisitions through May-26 and has no matching E6 (OP8-2015). Deal B's consolidated EBITDA includes DBW and is read in Part 06. Wellness clinic and emergency and specialty hospital context rows are in the same note, are not pooled and are shown in Exhibit 9.94 (adjustment share) and Exhibit 9.97 (cash EBITDA and add-back recurrence)</t>
+          <t>Source: note C-61; Deal A rows from the 10-K public series DLA_EBITDA_E1 and DLA_EBITDA_ADJ_PUB; Deal C rows DLC-0019, DLC-4434 (E1), DLC-4426, DLC-4430 (E3), DLC-4107, DLC-4443 (Ares Credit Group cash EBITDA). ADJ_SHARE = (top rung − E1) ÷ top rung; E6 = D3 cash EBITDA (top rung less recurring cash "one-time" items). Basis: E1 A; E2/E3/E6 PF; Deal A E2m is a reconstruction from company-published non-GAAP items; Operator 2 E1 is compliance-certificate basis [M]. Clinic base ALL (consolidated). The E6/top median of 0.84 is across the eleven Operator 4, Operator 8, Operator 6 and Operator 3 readings. Operator 8's E6 is built from its as-owned adjusted EBITDA (E2m, OP8-1880) and is set against that rung; its E3 (OP8-2409) is fully pro forma for acquisitions through May-26 and has no matching E6 (OP8-2015). Deal B's consolidated EBITDA includes DBW and is read in Part 06. Wellness clinic and emergency and specialty hospital context rows are in the same note, are not pooled and are shown in Exhibit 9.94 (adjustment share) and Exhibit 9.97 (cash EBITDA and add-back recurrence)</t>
         </is>
       </c>
     </row>
@@ -25836,7 +25836,7 @@
     <row r="948">
       <c r="A948" s="8" t="inlineStr">
         <is>
-          <t>EV ÷ EBITDA at entry (x) of closed or signed core platform and scale transactions, by EBITDA rung and synergy treatment, 2012 to 2026; deal documents supplied by ABC Private Credit</t>
+          <t>EV ÷ EBITDA at entry (x) of closed or signed core platform and scale transactions, by EBITDA rung and synergy treatment, 2012 to 2026; deal documents supplied by Ares Credit Group</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit recap of GB Vet (Operator 2)</t>
+          <t>Ares Credit Group recap of GB Vet (Operator 2)</t>
         </is>
       </c>
       <c r="C960" s="7" t="inlineStr">
@@ -28145,7 +28145,7 @@
     <row r="1023">
       <c r="A1023" s="8" t="inlineStr">
         <is>
-          <t>Headline multiple (x), EV ($m), EBITDA rung, and leverage at close and after (x) for each platform transaction, Oct-14 to Aug-26; ABC Private Credit deal documents</t>
+          <t>Headline multiple (x), EV ($m), EBITDA rung, and leverage at close and after (x) for each platform transaction, Oct-14 to Aug-26; Ares Credit Group deal documents</t>
         </is>
       </c>
     </row>
@@ -28463,7 +28463,7 @@
       </c>
       <c r="B1030" s="7" t="inlineStr">
         <is>
-          <t>Operator 2 (GB Vet) — ABC Private Credit unitranche recap</t>
+          <t>Operator 2 (GB Vet) — Ares Credit Group unitranche recap</t>
         </is>
       </c>
       <c r="C1030" s="7" t="inlineStr">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="G1037" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit unitranche Feb-25: LEV_ST-59 0.93x gross / 0.59x net (E5 TTM Sep-24 $8.3m; sources differ)</t>
+          <t>Ares Credit Group unitranche Feb-25: LEV_ST-59 0.93x gross / 0.59x net (E5 TTM Sep-24 $8.3m; sources differ)</t>
         </is>
       </c>
       <c r="H1037" s="7" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="B1041" s="7" t="inlineStr">
         <is>
-          <t>Operator 3 — Sponsor 5 (ABC Private Credit proposal)</t>
+          <t>Operator 3 — Sponsor 5 (Ares Credit Group proposal)</t>
         </is>
       </c>
       <c r="C1041" s="7" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="G1042" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit proposal: 2.25x gross / 1.97x net (E5 run-rate $8.8m, P)</t>
+          <t>Ares Credit Group proposal: 2.25x gross / 1.97x net (E5 run-rate $8.8m, P)</t>
         </is>
       </c>
       <c r="H1042" s="7" t="inlineStr">
@@ -30178,7 +30178,7 @@
     <row r="1080">
       <c r="A1080" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 1 in each of ABC Private Credit's six areas, with period, basis and reference; clinic sheets FY08 to LTM Nov-17, FY2019 audit</t>
+          <t>The figure the document gives for Operator 1 in each of Ares Credit Group's six areas, with period, basis and reference; clinic sheets FY08 to LTM Nov-17, FY2019 audit</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30300,7 @@
       </c>
       <c r="B1086" s="7" t="inlineStr">
         <is>
-          <t>+8.8% on total clinic sales and +4.5% on retail in FY09. On the common clinic-level definition −0.3%, −1.6% and −4.0% in 2014–16, against +3.0%, +2.3% and +0.3% as presented to ABC Private Credit. On the common definition +0.4% in CY2019 and +7.0% in CY2022 (last of three in each) and −2.7% in 2020 (first of three).</t>
+          <t>+8.8% on total clinic sales and +4.5% on retail in FY09. On the common clinic-level definition −0.3%, −1.6% and −4.0% in 2014–16, against +3.0%, +2.3% and +0.3% as presented to Ares Credit Group. On the common definition +0.4% in CY2019 and +7.0% in CY2022 (last of three in each) and −2.7% in 2020 (first of three).</t>
         </is>
       </c>
       <c r="C1086" s="7" t="inlineStr">
@@ -30353,7 +30353,7 @@
     <row r="1091">
       <c r="A1091" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 2 and its Operator 10 seller chain in each of ABC Private Credit's six areas, with period, basis and reference; clinic data 2006 to LTM Mar-21, company decks to FY2025</t>
+          <t>The figure the document gives for Operator 2 and its Operator 10 seller chain in each of Ares Credit Group's six areas, with period, basis and reference; clinic data 2006 to LTM Mar-21, company decks to FY2025</t>
         </is>
       </c>
     </row>
@@ -30528,7 +30528,7 @@
     <row r="1102">
       <c r="A1102" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 4 (Operator 4 HoldCo) and Operator 9 in each of ABC Private Credit's six areas, with period, basis and reference; audits FY23 to FY25 and Q1-26; each cell names the company</t>
+          <t>The figure the document gives for Operator 4 (Operator 4 HoldCo) and Operator 9 in each of Ares Credit Group's six areas, with period, basis and reference; audits FY23 to FY25 and Q1-26; each cell names the company</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
     <row r="1113">
       <c r="A1113" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 5 in each of ABC Private Credit's six areas, with period, basis and reference; clinic tickets and units 2017 to Jun-23, clinic P&amp;L CY2020 to LTM Mar-23</t>
+          <t>The figure the document gives for Operator 5 in each of Ares Credit Group's six areas, with period, basis and reference; clinic tickets and units 2017 to Jun-23, clinic P&amp;L CY2020 to LTM Mar-23</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30878,7 @@
     <row r="1124">
       <c r="A1124" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 6 in each of ABC Private Credit's six areas, with period, basis and reference; company data 2021 to TTM Mar-26, 31 add-ons</t>
+          <t>The figure the document gives for Operator 6 in each of Ares Credit Group's six areas, with period, basis and reference; company data 2021 to TTM Mar-26, 31 add-ons</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
     <row r="1135">
       <c r="A1135" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 3 in each of ABC Private Credit's six areas, with period, basis and reference; clinic datacube Apr-21 to Aug-25 (surviving clinics)</t>
+          <t>The figure the document gives for Operator 3 in each of Ares Credit Group's six areas, with period, basis and reference; clinic datacube Apr-21 to Aug-25 (surviving clinics)</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31228,7 @@
     <row r="1146">
       <c r="A1146" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 7 State 05 segment in each of ABC Private Credit's six areas, with period, basis and reference; quality-of-earnings clinic P&amp;L Jan-23 to Jan-26, KPIs Jan-24 to Jun-26</t>
+          <t>The figure the document gives for Operator 7 State 05 segment in each of Ares Credit Group's six areas, with period, basis and reference; quality-of-earnings clinic P&amp;L Jan-23 to Jan-26, KPIs Jan-24 to Jun-26</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31350,7 @@
       </c>
       <c r="B1152" s="7" t="inlineStr">
         <is>
-          <t>On the common definition +11.4% (2025) and +4.8% (LTM Jun-26), against about 5.8% in an ABC Private Credit memo with no stated definition. No comparable year before 2025, and in no ranking.</t>
+          <t>On the common definition +11.4% (2025) and +4.8% (LTM Jun-26), against about 5.8% in an Ares Credit Group memo with no stated definition. No comparable year before 2025, and in no ranking.</t>
         </is>
       </c>
       <c r="C1152" s="7" t="inlineStr">
@@ -31403,7 +31403,7 @@
     <row r="1157">
       <c r="A1157" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 8 in each of ABC Private Credit's six areas, with period, basis and reference; clinic P&amp;L 2021 to LTM Mar-26, clinic-year volume 2021–24</t>
+          <t>The figure the document gives for Operator 8 in each of Ares Credit Group's six areas, with period, basis and reference; clinic P&amp;L 2021 to LTM Mar-26, clinic-year volume 2021–24</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
     <row r="1168">
       <c r="A1168" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal A in each of ABC Private Credit's six areas, with period, basis and reference; Forms 10-K FY1996 to FY26 and Q1 FY27 10-Q, clinic EBITDA FY23–23, clinic KPIs FY20 to Q1 FY27; operating measures only</t>
+          <t>The figure the document gives for Deal A in each of Ares Credit Group's six areas, with period, basis and reference; Forms 10-K FY1996 to FY26 and Q1 FY27 10-Q, clinic EBITDA FY23–23, clinic KPIs FY20 to Q1 FY27; operating measures only</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="1179">
       <c r="A1179" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal B's general practice and preventive operations (DLB) in each of ABC Private Credit's six areas, with period, basis and reference; clinic data Jan-23 to Aug-26; DBW excluded; operating measures only</t>
+          <t>The figure the document gives for Deal B's general practice and preventive operations (DLB) in each of Ares Credit Group's six areas, with period, basis and reference; clinic data Jan-23 to Aug-26; DBW excluded; operating measures only</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31928,7 @@
     <row r="1190">
       <c r="A1190" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal C in each of ABC Private Credit's six areas, with period, basis and reference; 2025 audit, site-level database Jan-22 to Jul-26, company KPIs; operating measures only</t>
+          <t>The figure the document gives for Deal C in each of Ares Credit Group's six areas, with period, basis and reference; 2025 audit, site-level database Jan-22 to Jul-26, company KPIs; operating measures only</t>
         </is>
       </c>
     </row>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="B1204" s="7" t="inlineStr">
         <is>
-          <t>FY24 / FY25: 19.4% / 26.8% on the clinics that survive to FY26 vs 27.2% / 34.3% on all clinics open at each year-end; FY26 28.7% on both; FY26 19.5% with co-op allocated to clinics at 5.15% of clinic sales (ABC Private Credit's basis; Part 05 section E)</t>
+          <t>FY24 / FY25: 19.4% / 26.8% on the clinics that survive to FY26 vs 27.2% / 34.3% on all clinics open at each year-end; FY26 28.7% on both; FY26 19.5% with co-op allocated to clinics at 5.15% of clinic sales (Ares Credit Group's basis; Part 05 section E)</t>
         </is>
       </c>
       <c r="C1204" s="7" t="inlineStr">
@@ -32991,12 +32991,12 @@
       </c>
       <c r="E1242" s="7" t="inlineStr">
         <is>
-          <t>6.2× 2018, rung n/s, A; 5.15× ABC Private Credit recap 2025, P (QL1-1729, QL1-1722)</t>
+          <t>6.2× 2018, rung n/s, A; 5.15× Ares Credit Group recap 2025, P (QL1-1729, QL1-1722)</t>
         </is>
       </c>
       <c r="F1242" s="7" t="inlineStr">
         <is>
-          <t>1L 3.69× gross on ABC Private Credit E5 LTM Oct-25, P; LV3 3.05× on E4 PF (QL1-1655, QL1-0498)</t>
+          <t>1L 3.69× gross on Ares Credit Group E5 LTM Oct-25, P; LV3 3.05× on E4 PF (QL1-1655, QL1-0498)</t>
         </is>
       </c>
     </row>
@@ -33669,7 +33669,7 @@
       </c>
       <c r="J1261" s="7" t="inlineStr">
         <is>
-          <t>0.76 LTM Sep-25 (ABC Private Credit cash EBITDA)</t>
+          <t>0.76 LTM Sep-25 (Ares Credit Group cash EBITDA)</t>
         </is>
       </c>
       <c r="K1261" s="7" t="inlineStr">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="B1323" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 2 — ABC Private Credit refinancing proposal</t>
+          <t>Wellness Clinic Operator 2 — Ares Credit Group refinancing proposal</t>
         </is>
       </c>
       <c r="C1323" s="7" t="inlineStr">
@@ -35564,7 +35564,7 @@
       </c>
       <c r="B1324" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 1 — 2025 recapitalisation (ABC Private Credit memo of 22 December 2025)</t>
+          <t>Wellness Clinic Operator 1 — 2025 recapitalisation (Ares Credit Group memo of 22 December 2025)</t>
         </is>
       </c>
       <c r="C1324" s="7" t="inlineStr">
@@ -37556,7 +37556,7 @@
     <row r="1420">
       <c r="A1420" s="7" t="inlineStr">
         <is>
-          <t>Clinic EBITDA including co-op allocated at 5.15% of clinic sales (ABC Private Credit's basis), FY26 (A; the 824 clinics kept after the second round PF)</t>
+          <t>Clinic EBITDA including co-op allocated at 5.15% of clinic sales (Ares Credit Group's basis), FY26 (A; the 824 clinics kept after the second round PF)</t>
         </is>
       </c>
       <c r="B1420" s="7" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="D1472" s="7" t="inlineStr">
         <is>
-          <t>Four-wall level and loss share (Operator 1 D1.1 R-CASH to Nov-17 vs Deal A R-OPONLY FY23–23: different rent code, no overlap); SSS (Operator 1 CLOSE-FWD 2019–22 vs Deal A survivor CLOSE-RETRO; Operator 1 2023–25 is an undefined SSS_ST-59 from the ABC Private Credit chart); volume (Operator 1 pharmacy units, not traffic, ending Nov-17); valuation (E4 platform multiples vs Deal A public EV on E1)</t>
+          <t>Four-wall level and loss share (Operator 1 D1.1 R-CASH to Nov-17 vs Deal A R-OPONLY FY23–23: different rent code, no overlap); SSS (Operator 1 CLOSE-FWD 2019–22 vs Deal A survivor CLOSE-RETRO; Operator 1 2023–25 is an undefined SSS_ST-59 from the Ares Credit Group chart); volume (Operator 1 pharmacy units, not traffic, ending Nov-17); valuation (E4 platform multiples vs Deal A public EV on E1)</t>
         </is>
       </c>
     </row>
@@ -39075,7 +39075,7 @@
       </c>
       <c r="B1497" s="7" t="inlineStr">
         <is>
-          <t>The panel's Operator 1 column equals ABC Private Credit's own OP1-048 chart to rounding, so it is not an independent source, and that series is contradicted by Operator 1 clinic-level SSS_CD in 2012, 2014–16 and 2020 (−0.2%, −0.3%, −1.6%, −4.0%, −2.7% against the panel's +3%, +3%, +3%, 0%, +2%) (OP1-5128, OP1-5130..5132, OP1-8857; OP4-0559..0567). The panel's Deal A 2013 value (−4%, OP4-0576) is a transcription error against the 10-K's −0.4% (DLA-0347). Deal A's public comp is SSS_ST-59; Operator 1' is SSS_CD (CLOSE-FWD) to 2022 and undefined SSS_ST-59 from 2023</t>
+          <t>The panel's Operator 1 column equals Ares Credit Group's own OP1-048 chart to rounding, so it is not an independent source, and that series is contradicted by Operator 1 clinic-level SSS_CD in 2012, 2014–16 and 2020 (−0.2%, −0.3%, −1.6%, −4.0%, −2.7% against the panel's +3%, +3%, +3%, 0%, +2%) (OP1-5128, OP1-5130..5132, OP1-8857; OP4-0559..0567). The panel's Deal A 2013 value (−4%, OP4-0576) is a transcription error against the 10-K's −0.4% (DLA-0347). Deal A's public comp is SSS_ST-59; Operator 1' is SSS_CD (CLOSE-FWD) to 2022 and undefined SSS_ST-59 from 2023</t>
         </is>
       </c>
       <c r="C1497" s="7" t="inlineStr">
@@ -40423,7 +40423,7 @@
       </c>
       <c r="D1559" s="7" t="inlineStr">
         <is>
-          <t>FY25 0.99 (E3 Accounting Firm 2 $24.2m, DLB-3901), 1.03 (Accounting Firm 2 $18.5m, DLB-3900), 1.13 (post-audit $10.1m, DLB-5250), E1 −$3.2m (DLB-3866); LTM Jul-26 0.78 (post-audit $14.0m, DLB-5599) / 0.76 (ABC Private Credit E5, DLB-6300), E1 $1.22m (DLB-5644)</t>
+          <t>FY25 0.99 (E3 Accounting Firm 2 $24.2m, DLB-3901), 1.03 (Accounting Firm 2 $18.5m, DLB-3900), 1.13 (post-audit $10.1m, DLB-5250), E1 −$3.2m (DLB-3866); LTM Jul-26 0.78 (post-audit $14.0m, DLB-5599) / 0.76 (Ares Credit Group E5, DLB-6300), E1 $1.22m (DLB-5644)</t>
         </is>
       </c>
       <c r="E1559" s="7" t="inlineStr">
@@ -40450,7 +40450,7 @@
       </c>
       <c r="D1560" s="7" t="inlineStr">
         <is>
-          <t>FY25 0.46 (A6-P5-008..010); LTM Jul-26 0.59 / 0.52 / 0.37 on post-audit pro forma / ABC Private Credit E5 / E2 (DLB-5645)</t>
+          <t>FY25 0.46 (A6-P5-008..010); LTM Jul-26 0.59 / 0.52 / 0.37 on post-audit pro forma / Ares Credit Group E5 / E2 (DLB-5645)</t>
         </is>
       </c>
       <c r="E1560" s="7" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="D1562" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash $5.68m ÷ E5 0.43; ÷ post-audit pro forma 0.34 (DLB-6300/6302; DLB-5599)</t>
+          <t>Ares Credit Group cash $5.68m ÷ E5 0.43; ÷ post-audit pro forma 0.34 (DLB-6300/6302; DLB-5599)</t>
         </is>
       </c>
       <c r="E1562" s="7" t="inlineStr">
@@ -40543,7 +40543,7 @@
     <row r="1564" ht="39" customHeight="1">
       <c r="A1564" s="9" t="inlineStr">
         <is>
-          <t>Source: Rows as shown in each cell; Deal B Financing Model Jul-26 RF (DLB-008), QoE Workbook (DLB-022) and ABC Private Credit model vRF 09 (DLB-027); peer tables as referenced; note C-39 · Basis: Adjusted EBITDA rungs as labelled (E1 reported; E2, E3 and E5 adjusted, PF); Deal B's EBITDA rungs are consolidated, DBW included (DBW is read in Part 06 section F); maintenance capex is each company's own split [M]; peers' top rungs differ</t>
+          <t>Source: Rows as shown in each cell; Deal B Financing Model Jul-26 RF (DLB-008), QoE Workbook (DLB-022) and Ares Credit Group model vRF 09 (DLB-027); peer tables as referenced; note C-39 · Basis: Adjusted EBITDA rungs as labelled (E1 reported; E2, E3 and E5 adjusted, PF); Deal B's EBITDA rungs are consolidated, DBW included (DBW is read in Part 06 section F); maintenance capex is each company's own split [M]; peers' top rungs differ</t>
         </is>
       </c>
     </row>
@@ -40805,7 +40805,7 @@
       </c>
       <c r="B1583" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 2 add-ons 4.4x at close (A, as stated by the company [M]; QL2-1038); QL1 2025 5.15x (P, ABC Private Credit QoE; QL1-1722); JLI franchisees 5.8x (2023) and 6.3x LOI (2024) (rung n/s; QL1-1736/1735); QL1 2018 6.2x (QL1-1729)</t>
+          <t>Wellness Clinic Operator 2 add-ons 4.4x at close (A, as stated by the company [M]; QL2-1038); QL1 2025 5.15x (P, Ares Credit Group QoE; QL1-1722); JLI franchisees 5.8x (2023) and 6.3x LOI (2024) (rung n/s; QL1-1736/1735); QL1 2018 6.2x (QL1-1729)</t>
         </is>
       </c>
       <c r="C1583" s="7" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="B1666" s="7" t="inlineStr">
         <is>
-          <t>$4.7m ($1.4m ex $3.4m non-cash earn-out credit; Accounting Firm 1 "reported" $4.0m, as quoted from the QoE in ABC Private Credit's Internal Diligence Exhibits (the QoE itself was not supplied), omits a $1.0m impairment)</t>
+          <t>$4.7m ($1.4m ex $3.4m non-cash earn-out credit; Accounting Firm 1 "reported" $4.0m, as quoted from the QoE in Ares Credit Group's Internal Diligence Exhibits (the QoE itself was not supplied), omits a $1.0m impairment)</t>
         </is>
       </c>
       <c r="C1666" s="7" t="inlineStr">
@@ -42229,7 +42229,7 @@
     <row r="1668">
       <c r="A1668" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit underwriting (E5), LTM Sep-26E (P) / sponsor pro forma, LTM Sep-26E (P)</t>
+          <t>Ares Credit Group underwriting (E5), LTM Sep-26E (P) / sponsor pro forma, LTM Sep-26E (P)</t>
         </is>
       </c>
       <c r="B1668" s="7" t="inlineStr">
@@ -42263,7 +42263,7 @@
     <row r="1670">
       <c r="A1670" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, LTM Apr-26</t>
+          <t>Ares Credit Group cash EBITDA, LTM Apr-26</t>
         </is>
       </c>
       <c r="B1670" s="7" t="inlineStr">
@@ -43519,7 +43519,7 @@
     <row r="1724">
       <c r="A1724" s="7" t="inlineStr">
         <is>
-          <t>E5 ABC Private Credit, LTM Sep-26E (P)</t>
+          <t>E5 Ares Credit Group, LTM Sep-26E (P)</t>
         </is>
       </c>
       <c r="B1724" s="7" t="inlineStr">
@@ -43585,7 +43585,7 @@
     <row r="1727">
       <c r="A1727" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA (EB_CASH_ST-59, ABC Private Credit), LTM Apr-26 — not E6</t>
+          <t>Ares Credit Group cash EBITDA (EB_CASH_ST-59, Ares Credit Group), LTM Apr-26 — not E6</t>
         </is>
       </c>
       <c r="B1727" s="7" t="inlineStr">
@@ -44147,7 +44147,7 @@
     <row r="1756">
       <c r="A1756" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 LTM Sep-26 $71.7m (P), at close</t>
+          <t>Ares Credit Group E5 LTM Sep-26 $71.7m (P), at close</t>
         </is>
       </c>
       <c r="B1756" s="7" t="inlineStr">
@@ -44204,7 +44204,7 @@
       </c>
       <c r="F1757" s="7" t="inlineStr">
         <is>
-          <t>DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants; inputs from DLA-024 (ABC Private Credit Deal A Model v24) [I]</t>
+          <t>DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants; inputs from DLA-024 (Ares Credit Group Deal A Model v24) [I]</t>
         </is>
       </c>
     </row>
@@ -44226,7 +44226,7 @@
       </c>
       <c r="D1758" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit "rent-adjusted" 4.64x counts finance leases twice; ABC Private Credit v24 covenant line 4.46x (FQ3'27, net, capped cash); reading (a) 3.81x, and 4.47x if the $17.4m of gains is excluded</t>
+          <t>Ares Credit Group "rent-adjusted" 4.64x counts finance leases twice; Ares Credit Group v24 covenant line 4.46x (FQ3'27, net, capped cash); reading (a) 3.81x, and 4.47x if the $17.4m of gains is excluded</t>
         </is>
       </c>
       <c r="E1758" s="7" t="inlineStr">
@@ -44243,7 +44243,7 @@
     <row r="1759" ht="65" customHeight="1">
       <c r="A1759" s="9" t="inlineStr">
         <is>
-          <t>Source: note C-81 (FY2026, FY2026 ex-gains, LTM Jun-26 rows); Exhibit 9.76; fact rows as listed; DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants, for the covenant constructions. LV1 = bank and mortgage debt; LV3 adds finance leases and financing obligations ($194.3m FY26, DLA-0471; $196.6m Jun-26, A8-P5-089); LV5_6X adds 6 × operating-lease cash payments over E1 + rent; LV6 adds supplier finance. LTM LV5/LV6 on E1 are not computable because the 10-Q omits quarterly operating-lease cash payments [note C-81]. Charted in Exhibit 9.154 · Basis: Audited rungs A; company EBITDA PF; ABC Private Credit's EBITDA and covenant constructions P</t>
+          <t>Source: note C-81 (FY2026, FY2026 ex-gains, LTM Jun-26 rows); Exhibit 9.76; fact rows as listed; DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants, for the covenant constructions. LV1 = bank and mortgage debt; LV3 adds finance leases and financing obligations ($194.3m FY26, DLA-0471; $196.6m Jun-26, A8-P5-089); LV5_6X adds 6 × operating-lease cash payments over E1 + rent; LV6 adds supplier finance. LTM LV5/LV6 on E1 are not computable because the 10-Q omits quarterly operating-lease cash payments [note C-81]. Charted in Exhibit 9.154 · Basis: Audited rungs A; company EBITDA PF; Ares Credit Group's EBITDA and covenant constructions P</t>
         </is>
       </c>
     </row>
@@ -44332,7 +44332,7 @@
     <row r="1768">
       <c r="A1768" s="8" t="inlineStr">
         <is>
-          <t>Minimum quarter-average liquidity, $m, and the quarter it falls in, October 2026 to September 2030; management plan as in ABC Private Credit model v24; covenant $21.5m of average daily Liquidity</t>
+          <t>Minimum quarter-average liquidity, $m, and the quarter it falls in, October 2026 to September 2030; management plan as in Ares Credit Group model v24; covenant $21.5m of average daily Liquidity</t>
         </is>
       </c>
     </row>
@@ -44361,7 +44361,7 @@
     <row r="1770">
       <c r="A1770" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: $4.3m, April 2027 to March 2028</t>
+          <t>Ares Credit Group's model: $4.3m, April 2027 to March 2028</t>
         </is>
       </c>
       <c r="B1770" s="7" t="inlineStr">
@@ -44441,7 +44441,7 @@
     <row r="1774">
       <c r="A1774" s="7" t="inlineStr">
         <is>
-          <t>Lead case with EBITDA 9% below ABC Private Credit's model and no closure benefit</t>
+          <t>Lead case with EBITDA 9% below Ares Credit Group's model and no closure benefit</t>
         </is>
       </c>
       <c r="B1774" s="7" t="inlineStr">
@@ -44455,7 +44455,7 @@
     <row r="1775" ht="65" customHeight="1">
       <c r="A1775" s="9" t="inlineStr">
         <is>
-          <t>Source: CreditSwan monthly model of the proposed facilities (C-FIN-1, C-FIN-2); ABC Private Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28, 38, 103, 152; LW draft term sheet (21 September 2026), Credit Facilities, Use of Proceeds, Financial Covenants; Alpha - FY27 Clinic Closure Data, Summary!J33, J43 · Basis: P (projection on management's plan); monthly points, quarter average by daily interpolation between month-ends · Assumption: Every case carries $4.3m of professional fees, $25.5m of letters of credit, finance-lease interest charged to cash and the $7.4m December 2026 dividend. The shortfall is a uniform reduction of EBITDA in every period</t>
+          <t>Source: CreditSwan monthly model of the proposed facilities (C-FIN-1, C-FIN-2); Ares Credit Group Deal A Model v24, MODEL OUTPUT rows 13 to 28, 38, 103, 152; LW draft term sheet (21 September 2026), Credit Facilities, Use of Proceeds, Financial Covenants; Alpha - FY27 Clinic Closure Data, Summary!J33, J43 · Basis: P (projection on management's plan); monthly points, quarter average by daily interpolation between month-ends · Assumption: Every case carries $4.3m of professional fees, $25.5m of letters of credit, finance-lease interest charged to cash and the $7.4m December 2026 dividend. The shortfall is a uniform reduction of EBITDA in every period</t>
         </is>
       </c>
     </row>
@@ -44469,7 +44469,7 @@
     <row r="1778">
       <c r="A1778" s="8" t="inlineStr">
         <is>
-          <t>Refinancing capacity at maturity (September 2030) on observed anchors, by pairing of need and capacity, $m; LW draft term sheet (21 September 2026) and ABC Private Credit's Deal A model v24</t>
+          <t>Refinancing capacity at maturity (September 2030) on observed anchors, by pairing of need and capacity, $m; LW draft term sheet (21 September 2026) and Ares Credit Group's Deal A model v24</t>
         </is>
       </c>
     </row>
@@ -44518,7 +44518,7 @@
       </c>
       <c r="C1780" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit-model downside EBITDA $93.3m (P)</t>
+          <t>Ares Credit Group-model downside EBITDA $93.3m (P)</t>
         </is>
       </c>
       <c r="D1780" s="13" t="n">
@@ -44894,7 +44894,7 @@
     <row r="1793" ht="78" customHeight="1">
       <c r="A1793" s="9" t="inlineStr">
         <is>
-          <t>Source: Needs, cash flow available for debt service and downside EBITDA from the CreditSwan monthly model (C-FIN-1, C-FIN-3); multiples OP6-0031 (3.81x), OP1-7357 (4.27x), P5-S001 (5.97x), 8 closed gross first-lien prints from 3 platforms; spreads OP2-4336 (S+383), OP7-1164 (S+422), DLA-5593 (S+528), A8-S012 (S+534); SOFR 4.10% from ABC Private Credit Deal A Model v24, MODEL OUTPUT!L118; EBITDA rungs DLA-5864, A8-P5-092, DLA-0317, A8-P5-096 · Basis: Need P; actual rungs A and PF, held flat; downside EBITDA P. All results [I] · Assumption: Leverage leg = (multiple × EBITDA − $112.2m of finance leases at maturity) × 0.85. Coverage leg = cash flow available for debt service ÷ (cover × (SOFR + spread)) × 0.85. Need = bank debt less cash above a $13m reserve. Base path = lead case; downside = EBITDA 9% below ABC Private Credit's model in every period, no closure benefit</t>
+          <t>Source: Needs, cash flow available for debt service and downside EBITDA from the CreditSwan monthly model (C-FIN-1, C-FIN-3); multiples OP6-0031 (3.81x), OP1-7357 (4.27x), P5-S001 (5.97x), 8 closed gross first-lien prints from 3 platforms; spreads OP2-4336 (S+383), OP7-1164 (S+422), DLA-5593 (S+528), A8-S012 (S+534); SOFR 4.10% from Ares Credit Group Deal A Model v24, MODEL OUTPUT!L118; EBITDA rungs DLA-5864, A8-P5-092, DLA-0317, A8-P5-096 · Basis: Need P; actual rungs A and PF, held flat; downside EBITDA P. All results [I] · Assumption: Leverage leg = (multiple × EBITDA − $112.2m of finance leases at maturity) × 0.85. Coverage leg = cash flow available for debt service ÷ (cover × (SOFR + spread)) × 0.85. Need = bank debt less cash above a $13m reserve. Base path = lead case; downside = EBITDA 9% below Ares Credit Group's model in every period, no closure benefit</t>
         </is>
       </c>
     </row>
@@ -45384,7 +45384,7 @@
     <row r="1820" ht="30" customHeight="1">
       <c r="A1820" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.162 — Deal B needs EBITDA of $16.1–16.6m to refinance its term loan and delayed-draw loan at 4.3x in December 2030, against $11.16m on ABC Private Credit's measure today, and the near-term batch is $8.8–11.8m short of committed sources</t>
+          <t>Exhibit 9.162 — Deal B needs EBITDA of $16.1–16.6m to refinance its term loan and delayed-draw loan at 4.3x in December 2030, against $11.16m on Ares Credit Group's measure today, and the near-term batch is $8.8–11.8m short of committed sources</t>
         </is>
       </c>
     </row>
@@ -45450,12 +45450,12 @@
       </c>
       <c r="E1823" s="7" t="inlineStr">
         <is>
-          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit), 0.61x (ABC Private Credit E5), 0.34x (E2) (DLB-9603..9607)</t>
+          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit), 0.61x (Ares Credit Group E5), 0.34x (E2) (DLB-9603..9607)</t>
         </is>
       </c>
       <c r="F1823" s="7" t="inlineStr">
         <is>
-          <t>1.08x on $14.6m; 0.73x with DDTL drawn; 0.02x on ABC Private Credit cash</t>
+          <t>1.08x on $14.6m; 0.73x with DDTL drawn; 0.02x on Ares Credit Group cash</t>
         </is>
       </c>
     </row>
@@ -45477,12 +45477,12 @@
       </c>
       <c r="D1824" s="7" t="inlineStr">
         <is>
-          <t>LV4 at close 7.59x on ABC Private Credit E5 (DLB-9355); 5.99x on $14.77m (DLB-9373)</t>
+          <t>LV4 at close 7.59x on Ares Credit Group E5 (DLB-9355); 5.99x on $14.77m (DLB-9373)</t>
         </is>
       </c>
       <c r="E1824" s="7" t="inlineStr">
         <is>
-          <t>7.85–8.25x on ABC Private Credit E5 and 6.00–6.35x on $14.77m, after and before scheduled term-loan and seller-note principal</t>
+          <t>7.85–8.25x on Ares Credit Group E5 and 6.00–6.35x on $14.77m, after and before scheduled term-loan and seller-note principal</t>
         </is>
       </c>
       <c r="F1824" s="7" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="E1825" s="7" t="inlineStr">
         <is>
-          <t>EBITDA of $16.1–16.6m refinances the term loan and DDTL at 4.3x; $18.6–24.6m refinances them plus HoldCo at 5.4–7.2x (revolver excluded); against $11.16m ABC Private Credit E5 and $13.79m post-audit today</t>
+          <t>EBITDA of $16.1–16.6m refinances the term loan and DDTL at 4.3x; $18.6–24.6m refinances them plus HoldCo at 5.4–7.2x (revolver excluded); against $11.16m Ares Credit Group E5 and $13.79m post-audit today</t>
         </is>
       </c>
       <c r="F1825" s="7" t="inlineStr"/>
@@ -45550,7 +45550,7 @@
     <row r="1827" ht="39" customHeight="1">
       <c r="A1827" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB-5662; DLB-5668; DLB-6246; DLB-6351; DLB-9111; DLB-9355; DLB-9373; DLB-9603..9611; peers OP7-1304, OP6-0141, OP8-2547, OP8-2819/2367, OP1-10730/10738; Exhibit 4.09; notes C-80 and C-FIN-5 · Basis: P for the structure at close and every forward figure; peer anchors as printed (A, PF or P). The last column holds only figures printed in the borrower's and ABC Private Credit's models</t>
+          <t>Source: DLB-5662; DLB-5668; DLB-6246; DLB-6351; DLB-9111; DLB-9355; DLB-9373; DLB-9603..9611; peers OP7-1304, OP6-0141, OP8-2547, OP8-2819/2367, OP1-10730/10738; Exhibit 4.09; notes C-80 and C-FIN-5 · Basis: P for the structure at close and every forward figure; peer anchors as printed (A, PF or P). The last column holds only figures printed in the borrower's and Ares Credit Group's models</t>
         </is>
       </c>
     </row>
@@ -45776,7 +45776,7 @@
     <row r="1842" ht="45" customHeight="1">
       <c r="A1842" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.164 — Option Two covers its fixed charges only on EBITDA that includes forecast months (0.96x on ABC Private Credit's $29.4m); on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back it computes at 0.77x, against a $26.0m cash breakeven (LTM April and September 2026E)</t>
+          <t>Exhibit 9.164 — Option Two covers its fixed charges only on EBITDA that includes forecast months (0.96x on Ares Credit Group's $29.4m); on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back it computes at 0.77x, against a $26.0m cash breakeven (LTM April and September 2026E)</t>
         </is>
       </c>
     </row>
@@ -45834,7 +45834,7 @@
     <row r="1846">
       <c r="A1846" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA as printed $23.2m (LTM Apr-26, PF)</t>
+          <t>Ares Credit Group cash EBITDA as printed $23.2m (LTM Apr-26, PF)</t>
         </is>
       </c>
       <c r="B1846" s="7" t="inlineStr">
@@ -45856,7 +45856,7 @@
     <row r="1847">
       <c r="A1847" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m (LTM Apr-26, PF)</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m (LTM Apr-26, PF)</t>
         </is>
       </c>
       <c r="B1847" s="7" t="inlineStr">
@@ -45878,7 +45878,7 @@
     <row r="1848">
       <c r="A1848" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit $29.4m (E5, LTM Sep-26E, P)</t>
+          <t>Ares Credit Group $29.4m (E5, LTM Sep-26E, P)</t>
         </is>
       </c>
       <c r="B1848" s="7" t="inlineStr">
@@ -45951,7 +45951,7 @@
     <row r="1853" ht="45" customHeight="1">
       <c r="A1853" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.165 — At maturity in September 2032 Option Two leaves an $7.5m gap at the 4.3x median on ABC Private Credit's $29.4m growing 1.0% a year, and $59.3m on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); flat $29.4m clears only at 5.18x</t>
+          <t>Exhibit 9.165 — At maturity in September 2032 Option Two leaves an $7.5m gap at the 4.3x median on Ares Credit Group's $29.4m growing 1.0% a year, and $59.3m on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); flat $29.4m clears only at 5.18x</t>
         </is>
       </c>
     </row>
@@ -46245,7 +46245,7 @@
     <row r="1862">
       <c r="A1862" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1862" s="7" t="inlineStr">
@@ -46283,7 +46283,7 @@
     <row r="1863">
       <c r="A1863" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1863" s="7" t="inlineStr">
@@ -46321,7 +46321,7 @@
     <row r="1864">
       <c r="A1864" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1864" s="7" t="inlineStr">
@@ -46359,7 +46359,7 @@
     <row r="1865">
       <c r="A1865" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1865" s="7" t="inlineStr">
@@ -46397,7 +46397,7 @@
     <row r="1866">
       <c r="A1866" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1866" s="7" t="inlineStr">
@@ -46435,7 +46435,7 @@
     <row r="1867">
       <c r="A1867" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1867" s="7" t="inlineStr">
@@ -46546,7 +46546,7 @@
       </c>
       <c r="B1873" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1873" s="7" t="inlineStr">
@@ -46587,7 +46587,7 @@
       </c>
       <c r="B1874" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1874" s="7" t="inlineStr">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="B1875" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1875" s="7" t="inlineStr">
@@ -46669,7 +46669,7 @@
       </c>
       <c r="B1876" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1876" s="7" t="inlineStr">
@@ -46708,7 +46708,7 @@
       </c>
       <c r="B1877" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1877" s="7" t="inlineStr">
@@ -46747,7 +46747,7 @@
       </c>
       <c r="B1878" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1878" s="7" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="B1879" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1879" s="7" t="inlineStr">
@@ -46825,7 +46825,7 @@
       </c>
       <c r="B1880" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Ares Credit Group E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1880" s="7" t="inlineStr">
@@ -46864,7 +46864,7 @@
       </c>
       <c r="B1881" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1881" s="7" t="inlineStr">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="B1882" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1882" s="7" t="inlineStr">
@@ -46946,7 +46946,7 @@
       </c>
       <c r="B1883" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1883" s="7" t="inlineStr">
@@ -46987,7 +46987,7 @@
       </c>
       <c r="B1884" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1884" s="7" t="inlineStr">
@@ -47026,7 +47026,7 @@
       </c>
       <c r="B1885" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1885" s="7" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="B1886" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1886" s="7" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="B1887" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1887" s="7" t="inlineStr">
@@ -47143,7 +47143,7 @@
       </c>
       <c r="B1888" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Ares Credit Group cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1888" s="7" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="D1899" s="7" t="inlineStr">
         <is>
-          <t>Option One 5.30× on ABC Private Credit E5, LTM Sep-26E (DLC-4872, P); Option Two 5.96× on ABC Private Credit E5 (DLC-4725, P; equal to Option One's LV4 with the $21m sponsor debt, DLC-4878) and 5.61× on the sponsor's $32.3m (DLC-4711)</t>
+          <t>Option One 5.30× on Ares Credit Group E5, LTM Sep-26E (DLC-4872, P); Option Two 5.96× on Ares Credit Group E5 (DLC-4725, P; equal to Option One's LV4 with the $21m sponsor debt, DLC-4878) and 5.61× on the sponsor's $32.3m (DLC-4711)</t>
         </is>
       </c>
       <c r="E1899" s="7" t="inlineStr">
@@ -47402,7 +47402,7 @@
       </c>
       <c r="D1900" s="7" t="inlineStr">
         <is>
-          <t>14.8× sell-side (DLC-012-000514) / 16.59× ABC Private Credit (DLC-012-000515); LTM Sep-26E contains forecast months, P</t>
+          <t>14.8× sell-side (DLC-012-000514) / 16.59× Ares Credit Group (DLC-012-000515); LTM Sep-26E contains forecast months, P</t>
         </is>
       </c>
       <c r="E1900" s="7" t="inlineStr">
@@ -47428,7 +47428,7 @@
     <row r="1904">
       <c r="A1904" s="8" t="inlineStr">
         <is>
-          <t>Sensitivities that bear on the Deal A financing, set against observed ranges, on CreditSwan's monthly model of the LW draft term sheet (21 September 2026) and ABC Private Credit's Deal A model v24; liquidity in $m of minimum quarter-average, refinancing at September 2030</t>
+          <t>Sensitivities that bear on the Deal A financing, set against observed ranges, on CreditSwan's monthly model of the LW draft term sheet (21 September 2026) and Ares Credit Group's Deal A model v24; liquidity in $m of minimum quarter-average, refinancing at September 2030</t>
         </is>
       </c>
     </row>
@@ -47472,7 +47472,7 @@
       </c>
       <c r="C1906" s="7" t="inlineStr">
         <is>
-          <t>The term sheet limits the loan to the supplier-finance unwind and lets revolver loans fund it only if the loan is unavailable (LW draft term sheet (21 September 2026), Use of Proceeds); ABC Private Credit's model draws $86m and holds revolver loans at $67m (MODEL OUTPUT!D33:H34, C41:I41)</t>
+          <t>The term sheet limits the loan to the supplier-finance unwind and lets revolver loans fund it only if the loan is unavailable (LW draft term sheet (21 September 2026), Use of Proceeds); Ares Credit Group's model draws $86m and holds revolver loans at $67m (MODEL OUTPUT!D33:H34, C41:I41)</t>
         </is>
       </c>
       <c r="D1906" s="7" t="inlineStr">
@@ -47494,12 +47494,12 @@
       </c>
       <c r="B1907" s="7" t="inlineStr">
         <is>
-          <t>$36.6m spread over the remaining lease terms ($39.6m on ABC Private Credit's $4.3m figure); $21.0m inside four quarters</t>
+          <t>$36.6m spread over the remaining lease terms ($39.6m on Ares Credit Group's $4.3m figure); $21.0m inside four quarters</t>
         </is>
       </c>
       <c r="C1907" s="7" t="inlineStr">
         <is>
-          <t>Workbook: costs run to lease end, 42.1 months on average (Summary!J33, B49); ABC Private Credit's model: $4.3m, April 2027 to March 2028 (MODEL OUTPUT!F20:I20); the Diligence &amp; Structure Update (p.11) shows about $4.3m a year on a lease average of about five years</t>
+          <t>Workbook: costs run to lease end, 42.1 months on average (Summary!J33, B49); Ares Credit Group's model: $4.3m, April 2027 to March 2028 (MODEL OUTPUT!F20:I20); the Diligence &amp; Structure Update (p.11) shows about $4.3m a year on a lease average of about five years</t>
         </is>
       </c>
       <c r="D1907" s="7" t="inlineStr">
@@ -47509,7 +47509,7 @@
       </c>
       <c r="E1907" s="7" t="inlineStr">
         <is>
-          <t>Amount matters less than timing: paid as the leases run, the covenant is clear and minimum liquidity is about $1m below ABC Private Credit's figure; paid inside four quarters, for example to buy out the leases, it is about $17m lower and below the covenant</t>
+          <t>Amount matters less than timing: paid as the leases run, the covenant is clear and minimum liquidity is about $1m below Ares Credit Group's figure; paid inside four quarters, for example to buy out the leases, it is about $17m lower and below the covenant</t>
         </is>
       </c>
     </row>
@@ -47548,7 +47548,7 @@
       </c>
       <c r="B1909" s="7" t="inlineStr">
         <is>
-          <t>Liquidity covenant first breached at 6.6% (9.0% on ABC Private Credit's closure figure; 2.0% if the loan is drawn only when cash is short); leverage covenant at 46%; at 9% with no closure benefit liquidity is below $21.5m from the December 2027 quarter</t>
+          <t>Liquidity covenant first breached at 6.6% (9.0% on Ares Credit Group's closure figure; 2.0% if the loan is drawn only when cash is short); leverage covenant at 46%; at 9% with no closure benefit liquidity is below $21.5m from the December 2027 quarter</t>
         </is>
       </c>
       <c r="C1909" s="7" t="inlineStr">
@@ -47680,7 +47680,7 @@
       </c>
       <c r="D1917" s="7" t="inlineStr">
         <is>
-          <t>Rent treatment decides what the ratio measures [I]. Without rent in the denominator the ratio is 6.28x at close against 6.35x; in our illustrative cases the ABC Private Credit model v24 case would then sit above the level at the first test and the DDTL could not be drawn [I]. The EBITDAR (lease-consistent) reading is also the construction ABC Private Credit's model v24 uses (MODEL OUTPUT rows 52–46: 4.46x at the first quarterly test) [A]. The stock-compensation add-back loosens the covenant further and, in our illustrative downside, moves the Liquidity shortfall by two quarters [I].</t>
+          <t>Rent treatment decides what the ratio measures [I]. Without rent in the denominator the ratio is 6.28x at close against 6.35x; in our illustrative cases the Ares Credit Group model v24 case would then sit above the level at the first test and the DDTL could not be drawn [I]. The EBITDAR (lease-consistent) reading is also the construction Ares Credit Group's model v24 uses (MODEL OUTPUT rows 52–46: 4.46x at the first quarterly test) [A]. The stock-compensation add-back loosens the covenant further and, in our illustrative downside, moves the Liquidity shortfall by two quarters [I].</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="C1918" s="7" t="inlineStr">
         <is>
-          <t>The 6.35x–5.81x schedule sits well above the paths in our illustrative cases, in ABC Private Credit's model v24 and in CreditSwan's monthly lead case on that model, set out under 08 B earlier in this section (peak 4.53x, note C-FIN-1); on these levels the leverage covenant gives no earlier warning than Liquidity in any of our illustrative downside cases.</t>
+          <t>The 6.35x–5.81x schedule sits well above the paths in our illustrative cases, in Ares Credit Group's model v24 and in CreditSwan's monthly lead case on that model, set out under 08 B earlier in this section (peak 4.53x, note C-FIN-1); on these levels the leverage covenant gives no earlier warning than Liquidity in any of our illustrative downside cases.</t>
         </is>
       </c>
       <c r="D1918" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 path sits 27–35% below 6.35x–5.81x on an EBITDAR basis, and our illustrative base case would need a 42% EBITDA shortfall to reach the level [A/I]; Deal A's own annual EBITDA declines have been 11.9%, 6.7%, 23.5% and 19.9% on audited E1 (FY23–FY26), 33.2% on E1 excluding disposal gains in FY26, and 34% year on year in Q1 FY27 on company non-GAAP EBITDA (E2m, PF) [F/I].</t>
+          <t>Ares Credit Group's model v24 path sits 27–35% below 6.35x–5.81x on an EBITDAR basis, and our illustrative base case would need a 42% EBITDA shortfall to reach the level [A/I]; Deal A's own annual EBITDA declines have been 11.9%, 6.7%, 23.5% and 19.9% on audited E1 (FY23–FY26), 33.2% on E1 excluding disposal gains in FY26, and 34% year on year in Q1 FY27 on company non-GAAP EBITDA (E2m, PF) [F/I].</t>
         </is>
       </c>
     </row>
@@ -47715,12 +47715,12 @@
       </c>
       <c r="C1919" s="7" t="inlineStr">
         <is>
-          <t>As written, the DDTL condition appears to be tested at each draw, pro forma, on trailing EBITDA; the use of proceeds covers payments due within 107 days of each draw. It would help us to understand which reading ABC Private Credit intends.</t>
+          <t>As written, the DDTL condition appears to be tested at each draw, pro forma, on trailing EBITDA; the use of proceeds covers payments due within 107 days of each draw. It would help us to understand which reading Ares Credit Group intends.</t>
         </is>
       </c>
       <c r="D1919" s="7" t="inlineStr">
         <is>
-          <t>The SCF balance to be unwound is $140m, $177m or $184m depending on scope [I], and $122.6m of the SCF aging is already over 107 days, against the term sheet's 107-day eligibility language [F, SCF aging]. Testing each draw on trailing EBITDA can block funding without reducing leverage, because the draw replaces a payable [I]. In our illustrative base case (the quarterly model) the March 2027 draw passes at 4.76x (a 3.0% cushion), and in the monthly lead case on ABC Private Credit's model v24 at 4.60x (a 4.7% cushion) [I, C-FIN-1]; a one-quarter COVID-type shock at the start of the unwind exhausts base-case cash as written, but not when the test is applied once at close. At 5.15x our illustrative downside passes a once-at-close test by only 0.010x [I].</t>
+          <t>The SCF balance to be unwound is $140m, $177m or $184m depending on scope [I], and $122.6m of the SCF aging is already over 107 days, against the term sheet's 107-day eligibility language [F, SCF aging]. Testing each draw on trailing EBITDA can block funding without reducing leverage, because the draw replaces a payable [I]. In our illustrative base case (the quarterly model) the March 2027 draw passes at 4.76x (a 3.0% cushion), and in the monthly lead case on Ares Credit Group's model v24 at 4.60x (a 4.7% cushion) [I, C-FIN-1]; a one-quarter COVID-type shock at the start of the unwind exhausts base-case cash as written, but not when the test is applied once at close. At 5.15x our illustrative downside passes a once-at-close test by only 0.010x [I].</t>
         </is>
       </c>
     </row>
@@ -47740,7 +47740,7 @@
       </c>
       <c r="D1920" s="7" t="inlineStr">
         <is>
-          <t>While the $67m cap applies, with $44m drawn and $25.5m of letters of credit, availability is exactly $21.5m, the covenant minimum [I]. In our illustrative quarterly cases, which do not charge finance-lease interest, the ABC Private Credit model v24 case drawn as ABC Private Credit's model draws it ($86m, cap kept on) averages $13.2m of daily Liquidity in the September 2027 quarter, and $50m with $111m drawn [I]; in the monthly lead case on ABC Private Credit's model v24 (Exhibit 9.157) the full $111m is drawn by April 2027, the cap lifts and the September 2027 quarter averages $55.5m [I, C-FIN-1]. In our illustrative case on the 10-Q's SCF scope, without the build-up on the Lender 6 line and with a weak September quarter, Liquidity bottoms at $8.0m if the cap lifts when a draw is partly refused, and cash runs out in the September 2027 quarter if it does not [I].</t>
+          <t>While the $67m cap applies, with $44m drawn and $25.5m of letters of credit, availability is exactly $21.5m, the covenant minimum [I]. In our illustrative quarterly cases, which do not charge finance-lease interest, the Ares Credit Group model v24 case drawn as Ares Credit Group's model draws it ($86m, cap kept on) averages $13.2m of daily Liquidity in the September 2027 quarter, and $50m with $111m drawn [I]; in the monthly lead case on Ares Credit Group's model v24 (Exhibit 9.157) the full $111m is drawn by April 2027, the cap lifts and the September 2027 quarter averages $55.5m [I, C-FIN-1]. In our illustrative case on the 10-Q's SCF scope, without the build-up on the Lender 6 line and with a weak September quarter, Liquidity bottoms at $8.0m if the cap lifts when a draw is partly refused, and cash runs out in the September 2027 quarter if it does not [I].</t>
         </is>
       </c>
     </row>
@@ -47800,7 +47800,7 @@
       </c>
       <c r="D1923" s="7" t="inlineStr">
         <is>
-          <t>The December 2026 payment falls two quarters before our illustrative downside's Liquidity shortfall, and not paying it is what keeps our illustrative SCF-squeeze case above $21m ($25.5m against $18.4m); a fully used G&amp;A bucket releases dividends that take the management case below $21m [I]. The $12m run-rate second-round benefit [M, CIP p.1] is before up to $2.1–4.7m a year of stranded corporate overhead (an upper bound that assumes all of the overhead attributable to the 119 clinics stays behind) and $1.1–1.9m of stranded advertising (at Deal A's own 1.38% (FY25) to 2.36% (FY26) advertising-to-sales ratio on the 119 clinics' sales, Part 05 section D), and $3.4–4.3m of it rests on a 13% sales-recapture assumption that no peer has measured [I]. ABC Private Credit's model v24 FCCR of 1.23x at close excludes finance-lease interest; including it gives about 0.93x, below the 1.03x dividend gate [A/I].</t>
+          <t>The December 2026 payment falls two quarters before our illustrative downside's Liquidity shortfall, and not paying it is what keeps our illustrative SCF-squeeze case above $21m ($25.5m against $18.4m); a fully used G&amp;A bucket releases dividends that take the management case below $21m [I]. The $12m run-rate second-round benefit [M, CIP p.1] is before up to $2.1–4.7m a year of stranded corporate overhead (an upper bound that assumes all of the overhead attributable to the 119 clinics stays behind) and $1.1–1.9m of stranded advertising (at Deal A's own 1.38% (FY25) to 2.36% (FY26) advertising-to-sales ratio on the 119 clinics' sales, Part 05 section D), and $3.4–4.3m of it rests on a 13% sales-recapture assumption that no peer has measured [I]. Ares Credit Group's model v24 FCCR of 1.23x at close excludes finance-lease interest; including it gives about 0.93x, below the 1.03x dividend gate [A/I].</t>
         </is>
       </c>
     </row>
@@ -47915,12 +47915,12 @@
       </c>
       <c r="C1929" s="7" t="inlineStr">
         <is>
-          <t>The term sheet states the term loan's amortisation and gives the delayed-draw loans identical terms, without a separate DDTL amortisation schedule (our illustrative cases assume the term loan's 1%). ABC Private Credit's model v24 row 43 keeps the DDTL at cumulative draws and does not reflect the amortisation paid in row 31, and its cell I108 points to N36 rather than R36; separately, the finance-lease interest component is not charged to cash (MODEL OUTPUT!D30 and D171).</t>
+          <t>The term sheet states the term loan's amortisation and gives the delayed-draw loans identical terms, without a separate DDTL amortisation schedule (our illustrative cases assume the term loan's 1%). Ares Credit Group's model v24 row 43 keeps the DDTL at cumulative draws and does not reflect the amortisation paid in row 31, and its cell I108 points to N36 rather than R36; separately, the finance-lease interest component is not charged to cash (MODEL OUTPUT!D30 and D171).</t>
         </is>
       </c>
       <c r="D1929" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 overstates debt by $0.5–0.8m [I]. The finance-lease interest not charged to cash is $2.0m in Q3 FY27 and $28.4m cumulatively through FY31 [F, ABC Private Credit Deal A Model v24 MODEL OUTPUT!D30 =+D171-D22, D171].</t>
+          <t>Ares Credit Group's model v24 overstates debt by $0.5–0.8m [I]. The finance-lease interest not charged to cash is $2.0m in Q3 FY27 and $28.4m cumulatively through FY31 [F, Ares Credit Group Deal A Model v24 MODEL OUTPUT!D30 =+D171-D22, D171].</t>
         </is>
       </c>
     </row>
@@ -47940,7 +47940,7 @@
       </c>
       <c r="D1930" s="7" t="inlineStr">
         <is>
-          <t>On the 10-Q's SCF scope our illustrative base case falls below its Liquidity covenant at every unwind speed except a late run-off [I]. Recovery is a real-estate question: NOLV of $228m covers funded debt 1.27x at close only with the $152m of owned real estate (the company's estimate of fair market value, built on tax-assessed values; no third-party appraisal) [F/M, Diligence &amp; Structure Update p.36; ABC Private Credit Diligence Tracker, tab ABC Private Credit, J59]; without it NOLV is $76m — 0.43x at close and 0.24x at our illustrative base-case peak [I] — and at the maximum funded amount of $284m the facilities exceed NOLV by $58m (total commitments of $336m exceed it by $101.6m) [I].</t>
+          <t>On the 10-Q's SCF scope our illustrative base case falls below its Liquidity covenant at every unwind speed except a late run-off [I]. Recovery is a real-estate question: NOLV of $228m covers funded debt 1.27x at close only with the $152m of owned real estate (the company's estimate of fair market value, built on tax-assessed values; no third-party appraisal) [F/M, Diligence &amp; Structure Update p.36; Ares Credit Group Diligence Tracker, tab Ares Credit Group, J59]; without it NOLV is $76m — 0.43x at close and 0.24x at our illustrative base-case peak [I] — and at the maximum funded amount of $284m the facilities exceed NOLV by $58m (total commitments of $336m exceed it by $101.6m) [I].</t>
         </is>
       </c>
     </row>
@@ -47967,7 +47967,7 @@
     <row r="1932" ht="39" customHeight="1">
       <c r="A1932" s="9" t="inlineStr">
         <is>
-          <t>Source: DLA-023 (LW draft term sheet (21 September 2026)); ABC Private Credit Deal A Model v24; Deal A FY26 10-K and Q1 FY27 10-Q; Diligence &amp; Structure Update; Alpha - FY27 Clinic Closure Data; CreditSwan illustrative cases (quarterly model of the proposed facilities; notes C-FIN-6 and C-FIN-7) · Basis: Illustrative cases P; they take the finance-lease cash line as ABC Private Credit's model has it and do not charge its interest component; tags as marked in each cell</t>
+          <t>Source: DLA-023 (LW draft term sheet (21 September 2026)); Ares Credit Group Deal A Model v24; Deal A FY26 10-K and Q1 FY27 10-Q; Diligence &amp; Structure Update; Alpha - FY27 Clinic Closure Data; CreditSwan illustrative cases (quarterly model of the proposed facilities; notes C-FIN-6 and C-FIN-7) · Basis: Illustrative cases P; they take the finance-lease cash line as Ares Credit Group's model has it and do not charge its interest component; tags as marked in each cell</t>
         </is>
       </c>
     </row>
@@ -48394,7 +48394,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>The answer, the three theses side by side, what ABC Private Credit asked, the sector in brief, what holds across the deals, the evidence base, and what carries forward</t>
+          <t>The answer, the three theses side by side, what Ares Credit Group asked, the sector in brief, what holds across the deals, the evidence base, and what carries forward</t>
         </is>
       </c>
     </row>
@@ -48406,7 +48406,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's six industry questions, (i) to (vi), one section each</t>
+          <t>Ares Credit Group's six industry questions, (i) to (vi), one section each</t>
         </is>
       </c>
     </row>
@@ -48466,7 +48466,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>The proposed financings of the three deals, as observations for ABC Private Credit's own underwriting</t>
+          <t>The proposed financings of the three deals, as observations for Ares Credit Group's own underwriting</t>
         </is>
       </c>
     </row>
@@ -48716,7 +48716,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on ABC Private Credit's basis from 12.8% to 14.4% (FY26) (Part 05 section B, Part 05 section E)</t>
+          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in Ares Credit Group's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on Ares Credit Group's basis from 12.8% to 14.4% (FY26) (Part 05 section B, Part 05 section E)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -48807,12 +48807,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
+          <t>Partially supported (leans supported) — on Ares Credit Group's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on ABC Private Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
+          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on Ares Credit Group's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -49009,7 +49009,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m on wellness clinic multiples reaches ABC Private Credit's $44m only at its top (Part 06 section F)</t>
+          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m on wellness clinic multiples reaches Ares Credit Group's $44m only at its top (Part 06 section F)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -49137,7 +49137,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>$9.2m of ABC Private Credit's $29.4m (LTM September 2026E, P) is pre-acquisition and letter-of-intent earnings; cash EBITDA 0.28–0.31 of pro forma against a 0.73 peer median (Part 07 section D, Part 07 section F)</t>
+          <t>$9.2m of Ares Credit Group's $29.4m (LTM September 2026E, P) is pre-acquisition and letter-of-intent earnings; cash EBITDA 0.28–0.31 of pro forma against a 0.73 peer median (Part 07 section D, Part 07 section F)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -49188,14 +49188,14 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 1.06 — At October 2026 each of ABC Private Credit's thirteen asks has an answer here; the industry questions and the benchmark rest on up to eleven benchmark operators (thirteen for same-store sales), and the three theses hold in part</t>
+          <t>Exhibit 1.06 — At October 2026 each of Ares Credit Group's thirteen asks has an answer here; the industry questions and the benchmark rest on up to eleven benchmark operators (thirteen for same-store sales), and the three theses hold in part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ABC Private Credit's goals for the study, in ABC Private Credit's words (September 2026), our answer in one line, and where it is substantiated</t>
+          <t>Ares Credit Group's goals for the study, in Ares Credit Group's words (September 2026), our answer in one line, and where it is substantiated</t>
         </is>
       </c>
     </row>
@@ -49207,7 +49207,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>What ABC Private Credit asked</t>
+          <t>What Ares Credit Group asked</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -49454,7 +49454,7 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>The weakest clinics are an identifiable tail, and closing them lifts clinic margin; on ABC Private Credit's basis after finance-lease cost the clinics kept sit in the lower half of the peer band; traffic is falling across the clinics kept; the second round's value turns on how the company measures clinic contribution; the financing is read in Part 08 section B</t>
+          <t>The weakest clinics are an identifiable tail, and closing them lifts clinic margin; on Ares Credit Group's basis after finance-lease cost the clinics kept sit in the lower half of the peer band; traffic is falling across the clinics kept; the second round's value turns on how the company measures clinic contribution; the financing is read in Part 08 section B</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -49510,7 +49510,7 @@
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Source: ABC Private Credit's note "Pet Care Services Project" (goals G1 to G13); the answers are summarised from the supplies named in the last column, where their sources are given · Basis: Summary of the supplies named; readings are our reading on the evidence supplied to date · Assumption: A-01, A-02, A-03, A-10</t>
+          <t>Source: Ares Credit Group's note "Pet Care Services Project" (goals G1 to G13); the answers are summarised from the supplies named in the last column, where their sources are given · Basis: Summary of the supplies named; readings are our reading on the evidence supplied to date · Assumption: A-01, A-02, A-03, A-10</t>
         </is>
       </c>
     </row>
@@ -49524,7 +49524,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of the eight areas ABC Private Credit asked about, what is durable, temporary or company-specific, and how deep the evidence is; operator records from FY1996 to 2026</t>
+          <t>Our answer on each of the eight areas Ares Credit Group asked about, what is durable, temporary or company-specific, and how deep the evidence is; operator records from FY1996 to 2026</t>
         </is>
       </c>
     </row>
@@ -49863,7 +49863,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>On ABC Private Credit's basis, co-op included and finance-lease cost at book, 10.7% (FY26) and 12.5% for the clinics kept (pro forma): at the floor of the 10.7–17.4% peer range and in its lower half, indicatively; 5.4–7.9% before co-op, on a rent treatment no peer shares (Exhibit 1.12)</t>
+          <t>On Ares Credit Group's basis, co-op included and finance-lease cost at book, 10.7% (FY26) and 12.5% for the clinics kept (pro forma): at the floor of the 10.7–17.4% peer range and in its lower half, indicatively; 5.4–7.9% before co-op, on a rent treatment no peer shares (Exhibit 1.12)</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Does not transfer: each deal has a different set of valid comparators (Part 04 section F); Deal A's placement on ABC Private Credit's basis is indicative, as its co-op is allocated at a flat rate and its rent is at book</t>
+          <t>Does not transfer: each deal has a different set of valid comparators (Part 04 section F); Deal A's placement on Ares Credit Group's basis is indicative, as its co-op is allocated at a flat rate and its rent is at book</t>
         </is>
       </c>
     </row>
@@ -50754,7 +50754,7 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>The share falling below the 27–32% it has held in FY23 to FY26 before co-op, or below 19.5% (FY26) on ABC Private Credit's basis with co-op allocated to clinics (11.4% for the clinics kept after the second round)</t>
+          <t>The share falling below the 27–32% it has held in FY23 to FY26 before co-op, or below 19.5% (FY26) on Ares Credit Group's basis with co-op allocated to clinics (11.4% for the clinics kept after the second round)</t>
         </is>
       </c>
     </row>
@@ -50798,7 +50798,7 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Set out in Part 08, for ABC Private Credit's own underwriting</t>
+          <t>Set out in Part 08, for Ares Credit Group's own underwriting</t>
         </is>
       </c>
     </row>
@@ -51105,21 +51105,21 @@
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 3.01 — On the six measures ABC Private Credit asked about, volume has been flat and, outside 2020, steady, the ticket has carried growth and clinic margins before rebates moved within 1.3–5.4 points at each operator (FY08 to 2026); rebates, overhead and recurring acquisition costs make platform earnings and cash less steady</t>
+          <t>Exhibit 3.01 — On the six measures Ares Credit Group asked about, volume has been flat and, outside 2020, steady, the ticket has carried growth and clinic margins before rebates moved within 1.3–5.4 points at each operator (FY08 to 2026); rebates, overhead and recurring acquisition costs make platform earnings and cash less steady</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of ABC Private Credit's six industry questions, (i) to (vi), with the depth of the evidence and what would change it; operator records from FY1996 to 2026</t>
+          <t>Our answer on each of Ares Credit Group's six industry questions, (i) to (vi), with the depth of the evidence and what would change it; operator records from FY1996 to 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -51977,7 +51977,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>SSS_CD CLOSE-FWD; SSS_CO-PF 2018 and SSS_ST-59 ABC Private Credit 2023–25 (CLOSE-UNK)</t>
+          <t>SSS_CD CLOSE-FWD; SSS_CO-PF 2018 and SSS_ST-59 Ares Credit Group 2023–25 (CLOSE-UNK)</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -53102,14 +53102,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of ABC Private Credit's asks on multiples, leverage, the benchmark, the scope of wellness clinics and emergency and specialty hospitals, and what public sources add; transactions 2012–26, operator records to 2026 (the longest from FY1996, Deal A), public sources read on 30 September 2026 (census income 2020–2024)</t>
+          <t>Our answer on each of Ares Credit Group's asks on multiples, leverage, the benchmark, the scope of wellness clinics and emergency and specialty hospitals, and what public sources add; transactions 2012–26, operator records to 2026 (the longest from FY1996, Deal A), public sources read on 30 September 2026 (census income 2020–2024)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -53536,7 +53536,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Leverage at close (x) on financing EBITDA by rung and market environment: count, minimum, median and maximum of closed prints, proposals shown apart, 2014 to 2026; ABC Private Credit deal documents</t>
+          <t>Leverage at close (x) on financing EBITDA by rung and market environment: count, minimum, median and maximum of closed prints, proposals shown apart, 2014 to 2026; Ares Credit Group deal documents</t>
         </is>
       </c>
     </row>
@@ -55058,7 +55058,7 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Deal A's audited record, the longest in the files, shows a large general practice and pharmacy estate whose visits, clinic profit and reported margin fell together in the 2024 to 2026 soft period, with a third of clinics losing money in every year from FY23 to FY26 before co-op (19.5% in FY26 with co-op allocated to clinics, ABC Private Credit's basis).</t>
+          <t>Deal A's audited record, the longest in the files, shows a large general practice and pharmacy estate whose visits, clinic profit and reported margin fell together in the 2024 to 2026 soft period, with a third of clinics losing money in every year from FY23 to FY26 before co-op (19.5% in FY26 with co-op allocated to clinics, Ares Credit Group's basis).</t>
         </is>
       </c>
     </row>
@@ -55099,7 +55099,7 @@
     <row r="85" ht="39" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>Source: The eleven operator profiles in Part 09 section K, where each figure carries its references; Deal A's loss-making share on ABC Private Credit's basis from Part 05 section E · Basis: Each operator on its own best available data, period, rent code and clinic base; described, not ranked (Part 04 section E); live-deal profiles carry operating measures only · Assumption: A-01, A-02, A-07</t>
+          <t>Source: The eleven operator profiles in Part 09 section K, where each figure carries its references; Deal A's loss-making share on Ares Credit Group's basis from Part 05 section E · Basis: Each operator on its own best available data, period, rent code and clinic base; described, not ranked (Part 04 section E); live-deal profiles carry operating measures only · Assumption: A-01, A-02, A-07</t>
         </is>
       </c>
     </row>
@@ -56283,7 +56283,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>In this part the comparison departs from this: for Deal A, clinic margins are shown on ABC Private Credit's co-op-included basis and before co-op, with finance-lease cost labelled between them, and peers co-op-included on cash rent; each treatment is named and never pooled</t>
+          <t>In this part the comparison departs from this: for Deal A, clinic margins are shown on Ares Credit Group's co-op-included basis and before co-op, with finance-lease cost labelled between them, and peers co-op-included on cash rent; each treatment is named and never pooled</t>
         </is>
       </c>
     </row>
@@ -56334,7 +56334,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>$21.79m spread evenly over 42.1 months from April 2027, plus $4.3m of professional fees in ABC Private Credit's model in April to June 2027</t>
+          <t>$21.79m spread evenly over 42.1 months from April 2027, plus $4.3m of professional fees in Ares Credit Group's model in April to June 2027</t>
         </is>
       </c>
     </row>
@@ -56358,21 +56358,21 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.01 — Three of Deal A's four business components read partially supported, two of them leaning supported on ABC Private Credit's rebates-included basis; the second round's value turns on a definition Deal A has not yet given (evidence to October 2026)</t>
+          <t>Exhibit 5.01 — Three of Deal A's four business components read partially supported, two of them leaning supported on Ares Credit Group's rebates-included basis; the second round's value turns on a definition Deal A has not yet given (evidence to October 2026)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal A thesis (M1 to M5), with the depth of the evidence and what would change it; FY20 to the first quarter of FY27, files to 1 October 2026</t>
+          <t>Our reading on each component of Ares Credit Group's Deal A thesis (M1 to M5), with the depth of the evidence and what would change it; FY20 to the first quarter of FY27, files to 1 October 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -56399,12 +56399,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — the tail is identifiable and closing it lifts clinic margin; the decline across retained clinics is not addressed by closures. 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4%; with quartiles fixed at FY23, the top half's clinic EBITDA fell 16% to FY26 (Part 05 section B, Part 05 section E).</t>
+          <t>Partially supported (leans supported) — the tail is identifiable and closing it lifts clinic margin; the decline across retained clinics is not addressed by closures. 104 of the 119 second-round clinics sit in Ares Credit Group's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4%; with quartiles fixed at FY23, the top half's clinic EBITDA fell 16% to FY26 (Part 05 section B, Part 05 section E).</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Deal A's clinic-level earnings files FY23–FY26 and KPI files to the first quarter of FY27 (actual); the 119-clinic list of 1 October; co-op allocated at ABC Private Credit's rate; ABC Private Credit's quartile view reproduced exactly.</t>
+          <t>Deal A's clinic-level earnings files FY23–FY26 and KPI files to the first quarter of FY27 (actual); the 119-clinic list of 1 October; co-op allocated at Ares Credit Group's rate; Ares Credit Group's quartile view reproduced exactly.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -56448,7 +56448,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>The 119-clinic list (clinic results, rent, lease terms and cost to close, LTM June 2026); company estimates; ABC Private Credit's model; overhead ratios of three platforms, pro forma for two. No lease-exit plan.</t>
+          <t>The 119-clinic list (clinic results, rent, lease terms and cost to close, LTM June 2026); company estimates; Ares Credit Group's model; overhead ratios of three platforms, pro forma for two. No lease-exit plan.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -56465,7 +56465,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three. On ABC Private Credit's basis the clinic margin is 12.8% for all clinics and 14.4% for the 824 kept; after finance-lease cost, 10.7% and 12.5% against a 10.7–17.4% peer band (indicative); comparable traffic at the clinics kept −3.2% in FY26 against −2.0% to −2.8% (Part 05 section E).</t>
+          <t>Partially supported (leans supported) — on Ares Credit Group's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three. On Ares Credit Group's basis the clinic margin is 12.8% for all clinics and 14.4% for the 824 kept; after finance-lease cost, 10.7% and 12.5% against a 10.7–17.4% peer band (indicative); comparable traffic at the clinics kept −3.2% in FY26 against −2.0% to −2.8% (Part 05 section E).</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -56504,21 +56504,21 @@
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Source: Part 05 section A to Part 05 section G, and Part 08 section B for M5 · Basis: Mostly actual (A); clinic margins on ABC Private Credit's basis allocate co-op at a flat rate [I]; the second-round cases are pro forma run rates (PF) on the company's clinic measures; financing on the recapitalisation model of 29 September (P)</t>
+          <t>Source: Part 05 section A to Part 05 section G, and Part 08 section B for M5 · Basis: Mostly actual (A); clinic margins on Ares Credit Group's basis allocate co-op at a flat rate [I]; the second-round cases are pro forma run rates (PF) on the company's clinic measures; financing on the recapitalisation model of 29 September (P)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.02 — Deal A's weakest clinics are an identifiable tail and closing them lifts clinic margin, on ABC Private Credit's basis after finance-lease cost, to the lower half of the peer band; traffic is falling across the clinics it keeps and the second round's value turns on how the company measures clinic contribution (evidence to October 2026)</t>
+          <t>Exhibit 5.02 — Deal A's weakest clinics are an identifiable tail and closing them lifts clinic margin, on Ares Credit Group's basis after finance-lease cost, to the lower half of the peer band; traffic is falling across the clinics it keeps and the second round's value turns on how the company measures clinic contribution (evidence to October 2026)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>ABC Private Credit's thesis on Deal A by component: our reading on the evidence supplied to date, its basis, what holds, what does not and what would change it; FY23 to Q1 FY27, files to 1 October 2026</t>
+          <t>Ares Credit Group's thesis on Deal A by component: our reading on the evidence supplied to date, its basis, what holds, what does not and what would change it; FY23 to Q1 FY27, files to 1 October 2026</t>
         </is>
       </c>
     </row>
@@ -56567,12 +56567,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's quartile view reproduced exactly from the clinic files; 104 of the 119 second-round clinics in its bottom quartile; loss-making share including co-op 19.5% for all clinics, 11.4% for the 824 kept; quartiles fixed at FY23 for the same clinics (clinic-level EBITDA file; Data Cuts; FY27 Closing Clinics Financial Analysis)</t>
+          <t>Ares Credit Group's quartile view reproduced exactly from the clinic files; 104 of the 119 second-round clinics in its bottom quartile; loss-making share including co-op 19.5% for all clinics, 11.4% for the 824 kept; quartiles fixed at FY23 for the same clinics (clinic-level EBITDA file; Data Cuts; FY27 Closing Clinics Financial Analysis)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on ABC Private Credit's basis from 12.8% to 14.4% (FY26); rank is sticky (Part 05 section B, Part 05 section E)</t>
+          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in Ares Credit Group's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on Ares Credit Group's basis from 12.8% to 14.4% (FY26); rank is sticky (Part 05 section B, Part 05 section E)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -56658,7 +56658,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
+          <t>Partially supported (leans supported) — on Ares Credit Group's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -56668,7 +56668,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on ABC Private Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
+          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on Ares Credit Group's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -56717,21 +56717,21 @@
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Source: Deal A clinic-level EBITDA file FY23–FY26; New Deal A Data Cuts (Aug-26); FY27 Closing Clinics Financial Analysis (DLA-027); ABC Private Credit's Diligence &amp; Structure Update p.9; Project Alpha CIP p.1; Deal A FY26 10-K; Project Alpha Recapitalization Model v06 (DLA-026); each item as cited in the section named · Basis: A (filings, clinic files); clinic margins on ABC Private Credit's basis allocate co-op at a flat rate [I]; second-round cases pro forma (PF) on company clinic measures [F/I]; management plan (P); recapitalisation model (P) · Assumption: A-01, A-02, A-07, A-F2, A-P7</t>
+          <t>Source: Deal A clinic-level EBITDA file FY23–FY26; New Deal A Data Cuts (Aug-26); FY27 Closing Clinics Financial Analysis (DLA-027); Ares Credit Group's Diligence &amp; Structure Update p.9; Project Alpha CIP p.1; Deal A FY26 10-K; Project Alpha Recapitalization Model v06 (DLA-026); each item as cited in the section named · Basis: A (filings, clinic files); clinic margins on Ares Credit Group's basis allocate co-op at a flat rate [I]; second-round cases pro forma (PF) on company clinic measures [F/I]; management plan (P); recapitalisation model (P) · Assumption: A-01, A-02, A-07, A-F2, A-P7</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.10 — Spread over the 42.1-month average lease term, the workbook's $21.79m of closure cash is about $5.36m a year in FY28–FY31, against $4.3m in FY28 alone in ABC Private Credit's model</t>
+          <t>Exhibit 5.10 — Spread over the 42.1-month average lease term, the workbook's $21.79m of closure cash is about $5.36m a year in FY28–FY31, against $4.3m in FY28 alone in Ares Credit Group's model</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Second-round closure cost for 119 clinics by component and by fiscal year, $m: company workbook against ABC Private Credit model v24</t>
+          <t>Second-round closure cost for 119 clinics by component and by fiscal year, $m: company workbook against Ares Credit Group model v24</t>
         </is>
       </c>
     </row>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model</t>
+          <t>Ares Credit Group's model</t>
         </is>
       </c>
     </row>
@@ -56950,7 +56950,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: closure cash</t>
+          <t>Ares Credit Group's model: closure cash</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
@@ -56975,7 +56975,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: professional fees</t>
+          <t>Ares Credit Group's model: professional fees</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
@@ -57000,7 +57000,7 @@
     <row r="51" ht="52" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Source: Alpha - FY27 Clinic Closure Data, Summary!J32, J33, J37:J47, B49; ABC Private Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11; timing by fiscal year: C-FIN-4 · Basis: M (company estimate, a maximum before lease assignments); A (ABC Private Credit model). Timing [I] · Assumption: The workbook gives no clinic-by-clinic schedule; its cash is spread evenly over the average remaining term of 42.1 months from April 2027, the month ABC Private Credit's model starts the closure. Deferred maintenance and the owned clinics' six-month costs would fall earlier</t>
+          <t>Source: Alpha - FY27 Clinic Closure Data, Summary!J32, J33, J37:J47, B49; Ares Credit Group Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11; timing by fiscal year: C-FIN-4 · Basis: M (company estimate, a maximum before lease assignments); A (Ares Credit Group model). Timing [I] · Assumption: The workbook gives no clinic-by-clinic schedule; its cash is spread evenly over the average remaining term of 42.1 months from April 2027, the month Ares Credit Group's model starts the closure. Deferred maintenance and the owned clinics' six-month costs would fall earlier</t>
         </is>
       </c>
     </row>
@@ -57107,7 +57107,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit $4.3m of cash in FY28 plus $4.3m of fees</t>
+          <t>Ares Credit Group $4.3m of cash in FY28 plus $4.3m of fees</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -57122,7 +57122,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model differs in amount and in timing: the workbook (and ABC Private Credit's Diligence &amp; Structure Update, up to $21.5m) spreads the cash over the lease terms, about $5.3m a year from FY28 to FY31, against $4.3m in FY28 alone in ABC Private Credit's model; its effect on liquidity is in Part 08 section E; dark rent is the larger exposure in the one peer programme on file</t>
+          <t>Ares Credit Group's model differs in amount and in timing: the workbook (and Ares Credit Group's Diligence &amp; Structure Update, up to $21.5m) spreads the cash over the lease terms, about $5.3m a year from FY28 to FY31, against $4.3m in FY28 alone in Ares Credit Group's model; its effect on liquidity is in Part 08 section E; dark rent is the larger exposure in the one peer programme on file</t>
         </is>
       </c>
     </row>
@@ -57183,7 +57183,7 @@
     <row r="61" ht="39" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Source: Observed ranges of Part 03 and Part 04 with the fact rows and exhibits in each cell; Alpha - FY27 Clinic Closure Data, Summary!J33, J43, J59, B49; ABC Private Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11 · Basis: Readings on the observed ranges are [I]; alternative parameters are assumed; Deal A values are A except the plan (P) and the company's closure estimates (M) · Assumption: A-01, A-07, A-F2</t>
+          <t>Source: Observed ranges of Part 03 and Part 04 with the fact rows and exhibits in each cell; Alpha - FY27 Clinic Closure Data, Summary!J33, J43, J59, B49; Ares Credit Group Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11 · Basis: Readings on the observed ranges are [I]; alternative parameters are assumed; Deal A values are A except the plan (P) and the company's closure estimates (M) · Assumption: A-01, A-07, A-F2</t>
         </is>
       </c>
     </row>
@@ -57369,14 +57369,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal B thesis (MS1 to MS6), with the depth of the evidence and what would change it; January 2023 to August 2026</t>
+          <t>Our reading on each component of Ares Credit Group's Deal B thesis (MS1 to MS6), with the depth of the evidence and what would change it; January 2023 to August 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -57593,7 +57593,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Newest cohort 18.9% in its 2025 owned months (company 18%); older cohorts 7.6% and 8.6% on book rent (company 9% and 9%); first-year same-store sales −8.5% / −4.1% / −6.6% / −9.2% by cohort (company −13.3% to −6.2%); first owned year 0.55x / 0.76x / 0.71x of seller EBITDA against Operator 8 0.59–0.70x (DLB Datapack; DLB ABC Private Credit Diligence Responses p.2; Historical Acquisition Detail; Part 06 section B)</t>
+          <t>Newest cohort 18.9% in its 2025 owned months (company 18%); older cohorts 7.6% and 8.6% on book rent (company 9% and 9%); first-year same-store sales −8.5% / −4.1% / −6.6% / −9.2% by cohort (company −13.3% to −6.2%); first owned year 0.55x / 0.76x / 0.71x of seller EBITDA against Operator 8 0.59–0.70x (DLB Datapack; DLB Ares Credit Group Diligence Responses p.2; Historical Acquisition Detail; Part 06 section B)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -57625,7 +57625,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Median household income $63,374 against $47,928; three-attribute clinics 19.5% four-wall margin against 4.8% for those with none or one; density and acquisition returns not shown (ABC Private Credit Diligence Requests 8.21.26, attribution tabs; Part 06 section C). On public census data the 2025–26 clinics sit in markets with about twice the households within three miles and 8% higher household income than earlier clinics (93 of 103 clinics matched); the company's household figures are not on the same basis.</t>
+          <t>Median household income $63,374 against $47,928; three-attribute clinics 19.5% four-wall margin against 4.8% for those with none or one; density and acquisition returns not shown (Ares Credit Group Diligence Requests 8.21.26, attribution tabs; Part 06 section C). On public census data the 2025–26 clinics sit in markets with about twice the households within three miles and 8% higher household income than earlier clinics (93 of 103 clinics matched); the company's household figures are not on the same basis.</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -57721,7 +57721,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Four-wall −25.9% on the seller's same months (January–July 2026); visit count −11.5% a day in Q1, −16.1% in Q2, −17.3% a day in July; company windows −21.8% (August) and −15.6% (September) without weekly data; value $33–46m on wellness clinic multiples (DBW Datapack; DBW ABC Private Credit Diligence Responses; Part 06 section F)</t>
+          <t>Four-wall −25.9% on the seller's same months (January–July 2026); visit count −11.5% a day in Q1, −16.1% in Q2, −17.3% a day in July; company windows −21.8% (August) and −15.6% (September) without weekly data; value $33–46m on wellness clinic multiples (DBW Datapack; DBW Ares Credit Group Diligence Responses; Part 06 section F)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -57731,7 +57731,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m reaches ABC Private Credit's $44m only at its top (Part 06 section F)</t>
+          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m reaches Ares Credit Group's $44m only at its top (Part 06 section F)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -57775,7 +57775,7 @@
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Source: Sections B to G of this part, with the documents and rows cited there: Project Bravo DLB Datapack (DLB-003), Historical Acquisition Detail (DLB-029), QoE Workbook LTM Mar-26 (DLB-022), Financing Model Jul-26 RF (DLB-008), ABC Private Credit Diligence Requests 8.21.26 (DLB-028), DBW Datapack (DLB-002), DLB ABC Private Credit Diligence Responses (DLB-033), DBW ABC Private Credit Diligence Responses (DLB-034); public census data around 110 matched clinics [I, C-PUB-5]. The financing component is read in Part 08 section C · Basis: Reading labels as in Exhibit 1.05 and Exhibit 8.02. Figures are actual (A) unless marked; seller closing EBITDA and cash-rent margins are pro forma (PF); the borrower's plan is projected (P)</t>
+          <t>Source: Sections B to G of this part, with the documents and rows cited there: Project Bravo DLB Datapack (DLB-003), Historical Acquisition Detail (DLB-029), QoE Workbook LTM Mar-26 (DLB-022), Financing Model Jul-26 RF (DLB-008), Ares Credit Group Diligence Requests 8.21.26 (DLB-028), DBW Datapack (DLB-002), DLB Ares Credit Group Diligence Responses (DLB-033), DBW Ares Credit Group Diligence Responses (DLB-034); public census data around 110 matched clinics [I, C-PUB-5]. The financing component is read in Part 08 section C · Basis: Reading labels as in Exhibit 1.05 and Exhibit 8.02. Figures are actual (A) unless marked; seller closing EBITDA and cash-rent margins are pro forma (PF); the borrower's plan is projected (P)</t>
         </is>
       </c>
     </row>
@@ -58091,7 +58091,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Reporting and cash figures stated in the DLB ABC Private Credit Diligence Responses (1 October 2026) against the data files supplied; company figure, data figure and how far they tie</t>
+          <t>Reporting and cash figures stated in the DLB Ares Credit Group Diligence Responses (1 October 2026) against the data files supplied; company figure, data figure and how far they tie</t>
         </is>
       </c>
     </row>
@@ -58252,7 +58252,7 @@
     <row r="58" ht="39" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB ABC Private Credit Diligence Responses (DLB-033) pp.8–9; ABC Private Credit Diligence Requests 8.21.26 (DLB-028) tab 5; Financing Model (Jul-26 RF) (DLB-008) BS!C53; QoE Workbook LTM Mar-26 (DLB-022); Project Bravo DLB Datapack (DLB-003) · Basis: Company figures [M]; data figures as read [F] or computed [I]; actual (A)</t>
+          <t>Source: DLB Ares Credit Group Diligence Responses (DLB-033) pp.8–9; Ares Credit Group Diligence Requests 8.21.26 (DLB-028) tab 5; Financing Model (Jul-26 RF) (DLB-008) BS!C53; QoE Workbook LTM Mar-26 (DLB-022); Project Bravo DLB Datapack (DLB-003) · Basis: Company figures [M]; data figures as read [F] or computed [I]; actual (A)</t>
         </is>
       </c>
     </row>
@@ -58493,7 +58493,7 @@
     <row r="68" ht="52" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Source: Financing Model Jul-26 RF (DLB-008), consolidated income statement less the DBW segment and DBW corporate overhead tabs; QoE Workbook, 'DD #1 - Acquisition Expenses' (DLB-022); ABC Private Credit Diligence Requests, tab 6 (DLB-028); rows as shown; peers note C-26 · Basis: Now: A (LTM Mar-26) and PF (FY25 revenue); FY28E: P (borrower plan, including acquisitions not yet made); integration budget [M]; observed integration cost [I] on the like-for-like sub-lines named. DBW is read in Part 06 section F</t>
+          <t>Source: Financing Model Jul-26 RF (DLB-008), consolidated income statement less the DBW segment and DBW corporate overhead tabs; QoE Workbook, 'DD #1 - Acquisition Expenses' (DLB-022); Ares Credit Group Diligence Requests, tab 6 (DLB-028); rows as shown; peers note C-26 · Basis: Now: A (LTM Mar-26) and PF (FY25 revenue); FY28E: P (borrower plan, including acquisitions not yet made); integration budget [M]; observed integration cost [I] on the like-for-like sub-lines named. DBW is read in Part 06 section F</t>
         </is>
       </c>
     </row>
@@ -58507,7 +58507,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Figures stated in the DBW ABC Private Credit Diligence Responses (30 September 2026) against the DBW datapack and quality-of-earnings files; company figure, data figure and how far they tie</t>
+          <t>Figures stated in the DBW Ares Credit Group Diligence Responses (30 September 2026) against the DBW datapack and quality-of-earnings files; company figure, data figure and how far they tie</t>
         </is>
       </c>
     </row>
@@ -58690,7 +58690,7 @@
     <row r="80" ht="39" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>Source: DBW ABC Private Credit Diligence Responses (DLB-034) pp.1–4; DBW Datapack (Jul-26 RF) (DLB-002); DBW QoE workbook, 'DBW PF Adj. &amp; Walk' rows 11–49; Financing Model (Jul-26 RF) (DLB-008); Lender Update, 10 September 2026, p.3; Early Read p.6 · Basis: Company figures [M]; data figures as read [F] or computed [I]; the 2025 months are seller-system data</t>
+          <t>Source: DBW Ares Credit Group Diligence Responses (DLB-034) pp.1–4; DBW Datapack (Jul-26 RF) (DLB-002); DBW QoE workbook, 'DBW PF Adj. &amp; Walk' rows 11–49; Financing Model (Jul-26 RF) (DLB-008); Lender Update, 10 September 2026, p.3; Early Read p.6 · Basis: Company figures [M]; data figures as read [F] or computed [I]; the 2025 months are seller-system data</t>
         </is>
       </c>
     </row>
@@ -58973,17 +58973,17 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Post-audit pro forma $13.79m (DLB-5599); ABC Private Credit cash 0.34 of it (DLB-6302)</t>
+          <t>Post-audit pro forma $13.79m (DLB-5599); Ares Credit Group cash 0.34 of it (DLB-6302)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>$11.7m at the peer median; $5.7m at ABC Private Credit's own ratio</t>
+          <t>$11.7m at the peer median; $5.7m at Ares Credit Group's own ratio</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash-adjusted $5.7m only</t>
+          <t>Ares Credit Group cash-adjusted $5.7m only</t>
         </is>
       </c>
     </row>
@@ -59079,7 +59079,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>$5.9–6.3m × 5.3x = $37–38m; ABC Private Credit "$44m"</t>
+          <t>$5.9–6.3m × 5.3x = $37–38m; Ares Credit Group "$44m"</t>
         </is>
       </c>
     </row>
@@ -59133,12 +59133,12 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $11.16m</t>
+          <t>Ares Credit Group E5 $11.16m</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Up to 1.3x ABC Private Credit E5 if the "Action Needed" category closed with its full tail</t>
+          <t>Up to 1.3x Ares Credit Group E5 if the "Action Needed" category closed with its full tail</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -59329,14 +59329,14 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal C thesis (ST1 to ST4), with the depth of the evidence and what would change it; FY2025 to July 2026</t>
+          <t>Our reading on each component of Ares Credit Group's Deal C thesis (ST1 to ST4), with the depth of the evidence and what would change it; FY2025 to July 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -59407,12 +59407,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Insufficient evidence (underwriting EBITDA, E5; Accounting Firm 1 QoE absent) — cash earnings contradicted while the affiliate bonuses continue. $9.2m of ABC Private Credit's $29.4m is pre-acquisition and letter-of-intent earnings; cash EBITDA after recurring deal costs was 0.31 of pro forma in FY2025, and about 0.59 if the bonuses end (Part 07 section D).</t>
+          <t>Insufficient evidence (underwriting EBITDA, E5; Accounting Firm 1 QoE absent) — cash earnings contradicted while the affiliate bonuses continue. $9.2m of Ares Credit Group's $29.4m is pre-acquisition and letter-of-intent earnings; cash EBITDA after recurring deal costs was 0.31 of pro forma in FY2025, and about 0.59 if the bonuses end (Part 07 section D).</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>FY2025 audit (actual); ABC Private Credit's Internal Diligence Exhibits (pro forma and projected); the cash share at the roll-up peers; no quality-of-earnings report.</t>
+          <t>FY2025 audit (actual); Ares Credit Group's Internal Diligence Exhibits (pro forma and projected); the cash share at the roll-up peers; no quality-of-earnings report.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -59453,14 +59453,14 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 7.02 — FY2024 to LTM Sep-26E: Deal C's audited clinic margin holds; its 2026 trend, the claimed acquired-clinic uplift and its cash earnings are where the evidence falls short of ABC Private Credit's initial view</t>
+          <t>Exhibit 7.02 — FY2024 to LTM Sep-26E: Deal C's audited clinic margin holds; its 2026 trend, the claimed acquired-clinic uplift and its cash earnings are where the evidence falls short of Ares Credit Group's initial view</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Our reading of each component of ABC Private Credit's Deal C thesis on the evidence supplied to date, with its basis, what holds, what does not and what would change it; FY2024 to LTM Sep-26E</t>
+          <t>Our reading of each component of Ares Credit Group's Deal C thesis on the evidence supplied to date, with its basis, what holds, what does not and what would change it; FY2024 to LTM Sep-26E</t>
         </is>
       </c>
     </row>
@@ -60217,7 +60217,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Ares Credit Group asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -60266,12 +60266,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Contradicted — on trailing leverage, cover and funding. On ABC Private Credit's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
+          <t>Contradicted — on trailing leverage, cover and funding. On Ares Credit Group's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's response to the borrower's financing grid (19 September 2026) and the borrower's and ABC Private Credit's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
+          <t>Ares Credit Group's response to the borrower's financing grid (19 September 2026) and the borrower's and Ares Credit Group's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -60288,12 +60288,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Contradicted. The $204.3m first lien is 5.96x gross on ABC Private Credit's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
+          <t>Contradicted. The $204.3m first lien is 5.96x gross on Ares Credit Group's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
+          <t>Ares Credit Group's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -60310,7 +60310,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on ABC Private Credit's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
+          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on Ares Credit Group's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -60405,7 +60405,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; ABC Private Credit's Diligence &amp; Structure Update states that the sale process has been launched</t>
+          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; Ares Credit Group's Diligence &amp; Structure Update states that the sale process has been launched</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -60437,17 +60437,17 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m (term loan $55m); fixed-charge cover 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
+          <t>4.08x first lien and 7.59x with the HoldCo note on Ares Credit Group's $11.16m (term loan $55m); fixed-charge cover 0.61x on Ares Credit Group's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on ABC Private Credit's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
+          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on Ares Credit Group's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
+          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on Ares Credit Group's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -60474,17 +60474,17 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>5.96x gross first lien on ABC Private Credit's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
+          <t>5.96x gross first lien on Ares Credit Group's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on Ares Credit Group's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Cover computes at 0.96x on ABC Private Credit's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
+          <t>Cover computes at 0.96x on Ares Credit Group's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
+          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -60516,7 +60516,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Cover computes at 1.00x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
+          <t>Cover computes at 1.00x on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -60540,14 +60540,14 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in ABC Private Credit's model of September</t>
+          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in Ares Credit Group's model of September</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Main terms of the LW draft term sheet of 21 September 2026 (with ABC Private Credit's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
+          <t>Main terms of the LW draft term sheet of 21 September 2026 (with Ares Credit Group's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
         </is>
       </c>
     </row>
@@ -60593,7 +60593,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Revolver $44m deemed drawn; term loan $111m; ABC Private Credit's model v24: $152m of bank debt</t>
+          <t>Revolver $44m deemed drawn; term loan $111m; Ares Credit Group's model v24: $152m of bank debt</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -60661,7 +60661,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>1.9x first lien on ABC Private Credit's $71.7m (LTM Sep-26, including a forecast quarter)</t>
+          <t>1.9x first lien on Ares Credit Group's $71.7m (LTM Sep-26, including a forecast quarter)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -60729,7 +60729,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
+          <t>Ares Credit Group's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -60775,14 +60775,14 @@
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); ABC Private Credit Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
+          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); Ares Credit Group Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
+          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on Ares Credit Group's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
         </is>
       </c>
     </row>
@@ -60862,7 +60862,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>E5 ABC Private Credit LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
+          <t>E5 Ares Credit Group LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -60950,14 +60950,14 @@
     <row r="56" ht="39" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB-026 (ABC Private Credit response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
+          <t>Source: DLB-026 (Ares Credit Group response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on ABC Private Credit's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
+          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on Ares Credit Group's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
         </is>
       </c>
     </row>
@@ -61511,7 +61511,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Financing sensitivities of the Deal B and Deal C proposals: ABC Private Credit's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
+          <t>Financing sensitivities of the Deal B and Deal C proposals: Ares Credit Group's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
         </is>
       </c>
     </row>
@@ -61528,7 +61528,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit's case</t>
+          <t>Ares Credit Group's case</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -61560,7 +61560,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
+          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on Ares Credit Group's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -61575,7 +61575,7 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on ABC Private Credit's EBITDA (Part 08 section C)</t>
+          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on Ares Credit Group's EBITDA (Part 08 section C)</t>
         </is>
       </c>
     </row>
@@ -61592,7 +61592,7 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>FCCR_CD on ABC Private Credit's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
+          <t>FCCR_CD on Ares Credit Group's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -61602,12 +61602,12 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (ABC Private Credit's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
+          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (Ares Credit Group's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Cover is about 1x on the borrower's EBITDA and below 1x on ABC Private Credit's; the peer prints are on different definitions, so no position is taken</t>
+          <t>Cover is about 1x on the borrower's EBITDA and below 1x on Ares Credit Group's; the peer prints are on different definitions, so no position is taken</t>
         </is>
       </c>
     </row>
@@ -61634,12 +61634,12 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Total leverage 7.85–8.25x on ABC Private Credit's $11.16m and 6.00–6.35x on $14.77m</t>
+          <t>Total leverage 7.85–8.25x on Ares Credit Group's $11.16m and 6.00–6.35x on $14.77m</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>With EBITDA flat, total leverage on ABC Private Credit's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
+          <t>With EBITDA flat, total leverage on Ares Credit Group's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
         </is>
       </c>
     </row>
@@ -61671,7 +61671,7 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Both thresholds sit above today's $11.16m on ABC Private Credit's measure and $13.79m post-audit</t>
+          <t>Both thresholds sit above today's $11.16m on Ares Credit Group's measure and $13.79m post-audit</t>
         </is>
       </c>
     </row>
@@ -61688,7 +61688,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (ABC Private Credit model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
+          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (Ares Credit Group model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -61720,7 +61720,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Option Two's $204.3m first lien at 5.96x gross on ABC Private Credit's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
+          <t>Option Two's $204.3m first lien at 5.96x gross on Ares Credit Group's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -61730,7 +61730,7 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
+          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on Ares Credit Group's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -61752,7 +61752,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's coverage method on its cash EBITDA</t>
+          <t>Ares Credit Group's coverage method on its cash EBITDA</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -61784,7 +61784,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Option Two on ABC Private Credit's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
+          <t>Option Two on Ares Credit Group's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -61968,7 +61968,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Covenant levels well above the modelled path (4.53x peak on ABC Private Credit's model v24)</t>
+          <t>Covenant levels well above the modelled path (4.53x peak on Ares Credit Group's model v24)</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -62093,7 +62093,7 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per ABC Private Credit verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
+          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per Ares Credit Group verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -62188,7 +62188,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Delayed-draw amortisation; debt carried in ABC Private Credit's model v24</t>
+          <t>Delayed-draw amortisation; debt carried in Ares Credit Group's model v24</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
